--- a/GreenHerb/Matriz de rastreabilidade.xlsx
+++ b/GreenHerb/Matriz de rastreabilidade.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diogo\OneDrive\Ambiente de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6584D9C-2502-445D-B23E-A03DF5104DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68F18D5-671A-4240-8956-BA6BF6F04126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{909A9143-582B-4D53-990C-AFD6BBE7D058}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{909A9143-582B-4D53-990C-AFD6BBE7D058}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="223">
   <si>
     <t>ID</t>
   </si>
@@ -689,12 +689,78 @@
   <si>
     <t>Plano pontual + temperatura inválida</t>
   </si>
+  <si>
+    <t>TU-43</t>
+  </si>
+  <si>
+    <t>RN: justificação muito curta deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>Valores Limite (9 ch)</t>
+  </si>
+  <si>
+    <t>Retorna erro de tamanho</t>
+  </si>
+  <si>
+    <t>Justificação = "Curta"</t>
+  </si>
+  <si>
+    <t>TU-44</t>
+  </si>
+  <si>
+    <t>RN: justificação no limite mínimo deve ser aceite</t>
+  </si>
+  <si>
+    <t>Valores Limite (10 ch)</t>
+  </si>
+  <si>
+    <t>Justificação = "Dez letras"</t>
+  </si>
+  <si>
+    <t>TU-45</t>
+  </si>
+  <si>
+    <t>RN: justificação no limite máximo deve ser aceite</t>
+  </si>
+  <si>
+    <t>Valores Limite (500 ch)</t>
+  </si>
+  <si>
+    <t>Justificação = 500 chars</t>
+  </si>
+  <si>
+    <t>TU-46</t>
+  </si>
+  <si>
+    <t>MC/DC: plano não pontual não exige autorização</t>
+  </si>
+  <si>
+    <t>MC/DC</t>
+  </si>
+  <si>
+    <t>Tipo=regular, Auth=false</t>
+  </si>
+  <si>
+    <t>TI-05</t>
+  </si>
+  <si>
+    <t>RF: importação de catálogo via CSV</t>
+  </si>
+  <si>
+    <t>POST /herbs/import</t>
+  </si>
+  <si>
+    <t>Part. Equivalência</t>
+  </si>
+  <si>
+    <t>Ficheiro CSV válido</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -723,6 +789,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -744,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -753,6 +831,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -815,8 +899,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}" name="Tabela1" displayName="Tabela1" ref="B2:H48" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B2:H48" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}" name="Tabela1" displayName="Tabela1" ref="B2:H53" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B2:H53" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{5FFE78D4-90B0-4698-A26D-BEF2D31F1891}" name="ID" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{FC908435-E6B2-49F9-9C0A-FD430037704E}" name="Requisito / Regra" dataDxfId="5"/>
@@ -831,7 +915,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1147,16 +1231,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E031847A-75C8-407F-B2D5-2072BA2EA35A}">
-  <dimension ref="B2:R48"/>
-  <sheetFormatPr defaultColWidth="8.140625" defaultRowHeight="27" customHeight="1"/>
+  <dimension ref="B2:R53"/>
+  <sheetFormatPr defaultColWidth="8.15234375" defaultRowHeight="27" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.53515625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.84375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" customWidth="1"/>
-    <col min="7" max="7" width="27.85546875" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.84375" customWidth="1"/>
+    <col min="7" max="7" width="27.84375" customWidth="1"/>
+    <col min="8" max="8" width="20.69140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="36.75" customHeight="1">
@@ -1182,7 +1266,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="45">
+    <row r="3" spans="2:18" ht="43.75">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1206,7 +1290,7 @@
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="2:18" ht="45">
+    <row r="4" spans="2:18" ht="43.75">
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1229,7 +1313,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="45">
+    <row r="5" spans="2:18" ht="43.75">
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1253,7 +1337,7 @@
       </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="2:18" ht="45">
+    <row r="6" spans="2:18" ht="29.15">
       <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1276,7 +1360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="45">
+    <row r="7" spans="2:18" ht="43.75">
       <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1299,7 +1383,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="45">
+    <row r="8" spans="2:18" ht="29.15">
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
@@ -1322,7 +1406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="45">
+    <row r="9" spans="2:18" ht="43.75">
       <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1345,7 +1429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="45">
+    <row r="10" spans="2:18" ht="43.75">
       <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1368,7 +1452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="45">
+    <row r="11" spans="2:18" ht="43.75">
       <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
@@ -1392,7 +1476,7 @@
       </c>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="2:18" ht="45">
+    <row r="12" spans="2:18" ht="43.75">
       <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
@@ -1415,7 +1499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="45">
+    <row r="13" spans="2:18" ht="29.15">
       <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
@@ -1445,7 +1529,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="2:18" ht="45">
+    <row r="14" spans="2:18" ht="43.75">
       <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
@@ -1475,7 +1559,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="2:18" ht="45">
+    <row r="15" spans="2:18" ht="43.75">
       <c r="B15" s="2" t="s">
         <v>60</v>
       </c>
@@ -1505,7 +1589,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="2:18" ht="45">
+    <row r="16" spans="2:18" ht="29.15">
       <c r="B16" s="2" t="s">
         <v>65</v>
       </c>
@@ -1535,7 +1619,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="2:18" ht="45">
+    <row r="17" spans="2:18" ht="43.75">
       <c r="B17" s="2" t="s">
         <v>69</v>
       </c>
@@ -1565,7 +1649,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="2:18" ht="30">
+    <row r="18" spans="2:18" ht="29.15">
       <c r="B18" s="2" t="s">
         <v>73</v>
       </c>
@@ -1595,7 +1679,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="2:18" ht="30">
+    <row r="19" spans="2:18" ht="29.15">
       <c r="B19" s="2" t="s">
         <v>79</v>
       </c>
@@ -1625,7 +1709,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="2:18" ht="45">
+    <row r="20" spans="2:18" ht="29.15">
       <c r="B20" s="2" t="s">
         <v>83</v>
       </c>
@@ -1655,7 +1739,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="2:18" ht="45">
+    <row r="21" spans="2:18" ht="43.75">
       <c r="B21" s="2" t="s">
         <v>88</v>
       </c>
@@ -1685,7 +1769,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="2:18" ht="30">
+    <row r="22" spans="2:18" ht="29.15">
       <c r="B22" s="2" t="s">
         <v>93</v>
       </c>
@@ -1715,7 +1799,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="2:18" ht="45">
+    <row r="23" spans="2:18" ht="43.75">
       <c r="B23" s="2" t="s">
         <v>97</v>
       </c>
@@ -1745,7 +1829,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="2:18" ht="45">
+    <row r="24" spans="2:18" ht="29.15">
       <c r="B24" s="2" t="s">
         <v>101</v>
       </c>
@@ -1775,7 +1859,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="2:18" ht="45">
+    <row r="25" spans="2:18" ht="29.15">
       <c r="B25" s="2" t="s">
         <v>105</v>
       </c>
@@ -1805,7 +1889,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="2:18" ht="45">
+    <row r="26" spans="2:18" ht="29.15">
       <c r="B26" s="2" t="s">
         <v>110</v>
       </c>
@@ -1835,7 +1919,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="2:18" ht="30">
+    <row r="27" spans="2:18" ht="29.15">
       <c r="B27" s="2" t="s">
         <v>114</v>
       </c>
@@ -1865,7 +1949,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="2:18" ht="45">
+    <row r="28" spans="2:18" ht="29.15">
       <c r="B28" s="2" t="s">
         <v>118</v>
       </c>
@@ -1895,7 +1979,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="2:18" ht="45">
+    <row r="29" spans="2:18" ht="29.15">
       <c r="B29" s="2" t="s">
         <v>122</v>
       </c>
@@ -1925,7 +2009,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="2:18" ht="45">
+    <row r="30" spans="2:18" ht="43.75">
       <c r="B30" s="2" t="s">
         <v>126</v>
       </c>
@@ -1955,7 +2039,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="2:18" ht="45">
+    <row r="31" spans="2:18" ht="43.75">
       <c r="B31" s="2" t="s">
         <v>131</v>
       </c>
@@ -1985,7 +2069,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="2:18" ht="30">
+    <row r="32" spans="2:18" ht="29.15">
       <c r="B32" s="2" t="s">
         <v>135</v>
       </c>
@@ -2015,7 +2099,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="2:18" ht="45">
+    <row r="33" spans="2:18" ht="43.75">
       <c r="B33" s="2" t="s">
         <v>139</v>
       </c>
@@ -2045,7 +2129,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="2:18" ht="45">
+    <row r="34" spans="2:18" ht="43.75">
       <c r="B34" s="2" t="s">
         <v>143</v>
       </c>
@@ -2075,7 +2159,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="2:18" ht="30">
+    <row r="35" spans="2:18" ht="29.15">
       <c r="B35" s="2" t="s">
         <v>147</v>
       </c>
@@ -2105,7 +2189,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="2:18" ht="45">
+    <row r="36" spans="2:18" ht="43.75">
       <c r="B36" s="2" t="s">
         <v>152</v>
       </c>
@@ -2135,7 +2219,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="2:18" ht="45">
+    <row r="37" spans="2:18" ht="29.15">
       <c r="B37" s="2" t="s">
         <v>155</v>
       </c>
@@ -2165,7 +2249,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="2:18" ht="30">
+    <row r="38" spans="2:18" ht="29.15">
       <c r="B38" s="2" t="s">
         <v>159</v>
       </c>
@@ -2195,7 +2279,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="2:18" ht="45">
+    <row r="39" spans="2:18" ht="29.15">
       <c r="B39" s="2" t="s">
         <v>164</v>
       </c>
@@ -2225,7 +2309,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="2:18" ht="45">
+    <row r="40" spans="2:18" ht="29.15">
       <c r="B40" s="2" t="s">
         <v>167</v>
       </c>
@@ -2255,7 +2339,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="2:18" ht="45">
+    <row r="41" spans="2:18" ht="29.15">
       <c r="B41" s="2" t="s">
         <v>172</v>
       </c>
@@ -2285,7 +2369,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="2:18" ht="30">
+    <row r="42" spans="2:18" ht="29.15">
       <c r="B42" s="2" t="s">
         <v>176</v>
       </c>
@@ -2315,7 +2399,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="2:18" ht="45">
+    <row r="43" spans="2:18" ht="29.15">
       <c r="B43" s="2" t="s">
         <v>180</v>
       </c>
@@ -2345,7 +2429,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="2:18" ht="45">
+    <row r="44" spans="2:18" ht="29.15">
       <c r="B44" s="2" t="s">
         <v>184</v>
       </c>
@@ -2375,7 +2459,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="2:18" ht="45">
+    <row r="45" spans="2:18" ht="43.75">
       <c r="B45" s="2" t="s">
         <v>188</v>
       </c>
@@ -2398,7 +2482,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="2:18" ht="45">
+    <row r="46" spans="2:18" ht="29.15">
       <c r="B46" s="2" t="s">
         <v>191</v>
       </c>
@@ -2421,7 +2505,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="45">
+    <row r="47" spans="2:18" ht="43.75">
       <c r="B47" s="2" t="s">
         <v>193</v>
       </c>
@@ -2444,7 +2528,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="48" spans="2:18" ht="60">
+    <row r="48" spans="2:18" ht="43.75">
       <c r="B48" s="2" t="s">
         <v>196</v>
       </c>
@@ -2465,6 +2549,121 @@
       </c>
       <c r="H48" s="2" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="27" customHeight="1">
+      <c r="B49" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="27" customHeight="1">
+      <c r="B50" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="27" customHeight="1">
+      <c r="B51" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="27" customHeight="1">
+      <c r="B52" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="27" customHeight="1">
+      <c r="B53" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/GreenHerb/Matriz de rastreabilidade.xlsx
+++ b/GreenHerb/Matriz de rastreabilidade.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\GreenHerb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68F18D5-671A-4240-8956-BA6BF6F04126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB9D21-FB15-4BD6-9E47-BCCE45CC9148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{909A9143-582B-4D53-990C-AFD6BBE7D058}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="259">
   <si>
     <t>ID</t>
   </si>
@@ -754,6 +754,125 @@
   </si>
   <si>
     <t>Ficheiro CSV válido</t>
+  </si>
+  <si>
+    <t>TI-06</t>
+  </si>
+  <si>
+    <t>Upload sem ficheiro</t>
+  </si>
+  <si>
+    <t>Erro Forçado</t>
+  </si>
+  <si>
+    <t>Status 400 "Nenhum ficheiro enviado"</t>
+  </si>
+  <si>
+    <t>Nenhum ficherio enviado</t>
+  </si>
+  <si>
+    <t>TU-47</t>
+  </si>
+  <si>
+    <t>RN-02: Sensor com erro deve gerar alerta informativo</t>
+  </si>
+  <si>
+    <t>classifyAlert()</t>
+  </si>
+  <si>
+    <t>Caixa-Branca (MCC)</t>
+  </si>
+  <si>
+    <t>Retorna "Informativo"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sensor em estado </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>false</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-48</t>
+  </si>
+  <si>
+    <t>RN-02: Valor fora do limite com sensor OK (Aviso)</t>
+  </si>
+  <si>
+    <t>Retorna "Aviso"</t>
+  </si>
+  <si>
+    <t>Temp &gt; limite OU Hum &lt; limite</t>
+  </si>
+  <si>
+    <t>TU-49</t>
+  </si>
+  <si>
+    <t>RN-02: Valor excede limite crítico (Temp &gt; limite+5)</t>
+  </si>
+  <si>
+    <t>Retorna "Crítico"</t>
+  </si>
+  <si>
+    <t>Temp &gt; maxT + 5</t>
+  </si>
+  <si>
+    <t>TU-50</t>
+  </si>
+  <si>
+    <t>RN-02: Valores dentro dos limites e sensor OK</t>
+  </si>
+  <si>
+    <t>Retorna "Normal"</t>
+  </si>
+  <si>
+    <t>Todos os valores nominais</t>
+  </si>
+  <si>
+    <t>TU-51</t>
+  </si>
+  <si>
+    <t>RN-03: Ciclo de cultivo abaixo do limite (0 dias)</t>
+  </si>
+  <si>
+    <t>Retorna erro de ciclo</t>
+  </si>
+  <si>
+    <t>cycleDays = 0</t>
+  </si>
+  <si>
+    <t>TU-52</t>
+  </si>
+  <si>
+    <t>RN-03: Ciclo de cultivo no limite mínimo (1 dia)</t>
+  </si>
+  <si>
+    <t>cycleDays = 1</t>
+  </si>
+  <si>
+    <t>TU-53</t>
+  </si>
+  <si>
+    <t>RN-03: Ciclo de cultivo no limite máximo (365 dias)</t>
+  </si>
+  <si>
+    <t>cycleDays = 365</t>
+  </si>
+  <si>
+    <t>TU-54</t>
+  </si>
+  <si>
+    <t>RN-03: Ciclo de cultivo acima do limite (366 dias)</t>
+  </si>
+  <si>
+    <t>cycleDays = 366</t>
   </si>
 </sst>
 </file>
@@ -899,8 +1018,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}" name="Tabela1" displayName="Tabela1" ref="B2:H53" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B2:H53" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}" name="Tabela1" displayName="Tabela1" ref="B3:H64" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B3:H64" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{5FFE78D4-90B0-4698-A26D-BEF2D31F1891}" name="ID" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{FC908435-E6B2-49F9-9C0A-FD430037704E}" name="Requisito / Regra" dataDxfId="5"/>
@@ -1231,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E031847A-75C8-407F-B2D5-2072BA2EA35A}">
-  <dimension ref="B2:R53"/>
+  <dimension ref="B2:R64"/>
   <sheetFormatPr defaultColWidth="8.15234375" defaultRowHeight="27" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.53515625" customWidth="1"/>
@@ -1243,59 +1362,37 @@
     <col min="8" max="8" width="20.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:18" ht="36.75" customHeight="1"/>
+    <row r="3" spans="2:18" ht="14.6">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="2:18" ht="43.75">
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="2:18" ht="43.75">
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -1304,10 +1401,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -1315,10 +1412,10 @@
     </row>
     <row r="5" spans="2:18" ht="43.75">
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1327,22 +1424,22 @@
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="2:18" ht="29.15">
+    <row r="6" spans="2:18" ht="43.75">
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
@@ -1351,21 +1448,21 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="43.75">
+    <row r="7" spans="2:18" ht="29.15">
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
@@ -1374,21 +1471,21 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="29.15">
+    <row r="8" spans="2:18" ht="43.75">
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
@@ -1397,21 +1494,21 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="43.75">
+    <row r="9" spans="2:18" ht="29.15">
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -1420,10 +1517,10 @@
         <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>22</v>
@@ -1431,10 +1528,10 @@
     </row>
     <row r="10" spans="2:18" ht="43.75">
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -1443,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>37</v>
@@ -1454,10 +1551,10 @@
     </row>
     <row r="11" spans="2:18" ht="43.75">
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -1466,7 +1563,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>37</v>
@@ -1478,10 +1575,10 @@
     </row>
     <row r="12" spans="2:18" ht="43.75">
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -1490,21 +1587,21 @@
         <v>10</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="29.15">
+    <row r="13" spans="2:18" ht="43.75">
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -1513,13 +1610,13 @@
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1529,27 +1626,27 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="2:18" ht="43.75">
+    <row r="14" spans="2:18" ht="29.15">
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1561,10 +1658,10 @@
     </row>
     <row r="15" spans="2:18" ht="43.75">
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>55</v>
@@ -1573,13 +1670,13 @@
         <v>56</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1589,12 +1686,12 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="2:18" ht="29.15">
+    <row r="16" spans="2:18" ht="43.75">
       <c r="B16" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>55</v>
@@ -1603,13 +1700,13 @@
         <v>56</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1619,12 +1716,12 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="2:18" ht="43.75">
+    <row r="17" spans="2:18" ht="29.15">
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>55</v>
@@ -1633,13 +1730,13 @@
         <v>56</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -1649,27 +1746,27 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="2:18" ht="29.15">
+    <row r="18" spans="2:18" ht="43.75">
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1681,10 +1778,10 @@
     </row>
     <row r="19" spans="2:18" ht="29.15">
       <c r="B19" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>75</v>
@@ -1696,10 +1793,10 @@
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1711,10 +1808,10 @@
     </row>
     <row r="20" spans="2:18" ht="29.15">
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>75</v>
@@ -1723,13 +1820,13 @@
         <v>10</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -1739,12 +1836,12 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="2:18" ht="43.75">
+    <row r="21" spans="2:18" ht="29.15">
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>75</v>
@@ -1753,13 +1850,13 @@
         <v>10</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -1769,12 +1866,12 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="2:18" ht="29.15">
+    <row r="22" spans="2:18" ht="43.75">
       <c r="B22" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>75</v>
@@ -1783,13 +1880,13 @@
         <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1799,12 +1896,12 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="2:18" ht="43.75">
+    <row r="23" spans="2:18" ht="29.15">
       <c r="B23" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>75</v>
@@ -1813,13 +1910,13 @@
         <v>10</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -1829,12 +1926,12 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="2:18" ht="29.15">
+    <row r="24" spans="2:18" ht="43.75">
       <c r="B24" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>75</v>
@@ -1843,13 +1940,13 @@
         <v>10</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1861,10 +1958,10 @@
     </row>
     <row r="25" spans="2:18" ht="29.15">
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>75</v>
@@ -1873,13 +1970,13 @@
         <v>10</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1891,10 +1988,10 @@
     </row>
     <row r="26" spans="2:18" ht="29.15">
       <c r="B26" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>75</v>
@@ -1903,13 +2000,13 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1921,10 +2018,10 @@
     </row>
     <row r="27" spans="2:18" ht="29.15">
       <c r="B27" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>75</v>
@@ -1933,13 +2030,13 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1951,10 +2048,10 @@
     </row>
     <row r="28" spans="2:18" ht="29.15">
       <c r="B28" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>75</v>
@@ -1963,13 +2060,13 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -1981,10 +2078,10 @@
     </row>
     <row r="29" spans="2:18" ht="29.15">
       <c r="B29" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -1993,13 +2090,13 @@
         <v>10</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -2009,12 +2106,12 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="2:18" ht="43.75">
+    <row r="30" spans="2:18" ht="29.15">
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>75</v>
@@ -2023,13 +2120,13 @@
         <v>10</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -2041,10 +2138,10 @@
     </row>
     <row r="31" spans="2:18" ht="43.75">
       <c r="B31" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>75</v>
@@ -2053,13 +2150,13 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2069,12 +2166,12 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="2:18" ht="29.15">
+    <row r="32" spans="2:18" ht="43.75">
       <c r="B32" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>75</v>
@@ -2083,13 +2180,13 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -2099,12 +2196,12 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="2:18" ht="43.75">
+    <row r="33" spans="2:18" ht="29.15">
       <c r="B33" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>75</v>
@@ -2113,13 +2210,13 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2131,10 +2228,10 @@
     </row>
     <row r="34" spans="2:18" ht="43.75">
       <c r="B34" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>75</v>
@@ -2143,13 +2240,13 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -2159,27 +2256,27 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="2:18" ht="29.15">
+    <row r="35" spans="2:18" ht="43.75">
       <c r="B35" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -2189,12 +2286,12 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="2:18" ht="43.75">
+    <row r="36" spans="2:18" ht="29.15">
       <c r="B36" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>149</v>
@@ -2209,7 +2306,7 @@
         <v>150</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -2219,12 +2316,12 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="2:18" ht="29.15">
+    <row r="37" spans="2:18" ht="43.75">
       <c r="B37" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>149</v>
@@ -2236,10 +2333,10 @@
         <v>76</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -2251,10 +2348,10 @@
     </row>
     <row r="38" spans="2:18" ht="29.15">
       <c r="B38" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>149</v>
@@ -2263,13 +2360,13 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -2281,10 +2378,10 @@
     </row>
     <row r="39" spans="2:18" ht="29.15">
       <c r="B39" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>149</v>
@@ -2296,10 +2393,10 @@
         <v>161</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -2311,10 +2408,10 @@
     </row>
     <row r="40" spans="2:18" ht="29.15">
       <c r="B40" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>149</v>
@@ -2323,13 +2420,13 @@
         <v>10</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -2341,10 +2438,10 @@
     </row>
     <row r="41" spans="2:18" ht="29.15">
       <c r="B41" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>149</v>
@@ -2353,13 +2450,13 @@
         <v>10</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -2371,10 +2468,10 @@
     </row>
     <row r="42" spans="2:18" ht="29.15">
       <c r="B42" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>149</v>
@@ -2383,13 +2480,13 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>150</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -2401,10 +2498,10 @@
     </row>
     <row r="43" spans="2:18" ht="29.15">
       <c r="B43" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>149</v>
@@ -2413,13 +2510,13 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>150</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -2431,10 +2528,10 @@
     </row>
     <row r="44" spans="2:18" ht="29.15">
       <c r="B44" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>149</v>
@@ -2443,13 +2540,13 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -2459,12 +2556,12 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="2:18" ht="43.75">
+    <row r="45" spans="2:18" ht="29.15">
       <c r="B45" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>149</v>
@@ -2473,21 +2570,21 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" ht="29.15">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" ht="43.75">
       <c r="B46" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>149</v>
@@ -2499,18 +2596,18 @@
         <v>190</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" ht="43.75">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" ht="29.15">
       <c r="B47" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>149</v>
@@ -2522,18 +2619,18 @@
         <v>190</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>195</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="43.75">
       <c r="B48" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>149</v>
@@ -2542,44 +2639,44 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="27" customHeight="1">
+      <c r="B49" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G49" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H49" s="2" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="27" customHeight="1">
-      <c r="B49" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="27" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>75</v>
@@ -2588,21 +2685,21 @@
         <v>10</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="27" customHeight="1">
       <c r="B51" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>75</v>
@@ -2611,59 +2708,312 @@
         <v>10</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="27" customHeight="1">
       <c r="B52" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="27" customHeight="1">
       <c r="B53" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="27" customHeight="1">
+      <c r="B54" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="27" customHeight="1">
+      <c r="B55" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="27" customHeight="1">
+      <c r="B56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="27" customHeight="1">
+      <c r="B57" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" ht="27" customHeight="1">
+      <c r="B58" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="27" customHeight="1">
+      <c r="B59" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="27" customHeight="1">
+      <c r="B60" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="27" customHeight="1">
+      <c r="B61" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="27" customHeight="1">
+      <c r="B62" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" ht="27" customHeight="1">
+      <c r="B63" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="27" customHeight="1">
+      <c r="B64" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/GreenHerb/Matriz de rastreabilidade.xlsx
+++ b/GreenHerb/Matriz de rastreabilidade.xlsx
@@ -2,44 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\GreenHerb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\Engenharia-Software-II\GreenHerb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB9D21-FB15-4BD6-9E47-BCCE45CC9148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922F8FF2-DAB3-4885-A25D-A04B8EEEFB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{909A9143-582B-4D53-990C-AFD6BBE7D058}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="389">
   <si>
     <t>ID</t>
   </si>
@@ -194,53 +175,7 @@
     <t>Validação estrutural do token JWT</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">JWT contém </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>role</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> e </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>sessionId</t>
-    </r>
+    <t>JWT contém id, role e sessionId</t>
   </si>
   <si>
     <t>Login válido</t>
@@ -786,18 +721,7 @@
     <t>Retorna "Informativo"</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Sensor em estado </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>false</t>
-    </r>
+    <t>Sensor em estado false</t>
   </si>
   <si>
     <t>TU-48</t>
@@ -873,13 +797,403 @@
   </si>
   <si>
     <t>cycleDays = 366</t>
+  </si>
+  <si>
+    <t>TI-07</t>
+  </si>
+  <si>
+    <t>RF: criar plano regular válido</t>
+  </si>
+  <si>
+    <t>POST /plans</t>
+  </si>
+  <si>
+    <t>Tipo=regular, valores válidos</t>
+  </si>
+  <si>
+    <t>TI-08</t>
+  </si>
+  <si>
+    <t>RN: tipo de plano inválido deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>Tipo=experimental</t>
+  </si>
+  <si>
+    <t>TI-09</t>
+  </si>
+  <si>
+    <t>RN: temperatura fora do intervalo deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>Temperatura=17°C</t>
+  </si>
+  <si>
+    <t>TI-10</t>
+  </si>
+  <si>
+    <t>RN: humidade fora do intervalo deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>Humidade=39%</t>
+  </si>
+  <si>
+    <t>TI-11</t>
+  </si>
+  <si>
+    <t>RN: plano pontual sem autorização deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>Tipo=pontual, Auth=false</t>
+  </si>
+  <si>
+    <t>TI-12</t>
+  </si>
+  <si>
+    <t>RN: plano pontual autorizado deve ser aceite</t>
+  </si>
+  <si>
+    <t>Tipo=pontual, Auth=true</t>
+  </si>
+  <si>
+    <t>TI-13</t>
+  </si>
+  <si>
+    <t>Justificação &lt; 10 chars</t>
+  </si>
+  <si>
+    <t>TI-14</t>
+  </si>
+  <si>
+    <t>RF: criar lote válido</t>
+  </si>
+  <si>
+    <t>POST /batches</t>
+  </si>
+  <si>
+    <t>Lote com dados válidos</t>
+  </si>
+  <si>
+    <t>TI-15</t>
+  </si>
+  <si>
+    <t>RN: nome do lote é obrigatório</t>
+  </si>
+  <si>
+    <t>Name=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-16</t>
+  </si>
+  <si>
+    <t>RN: data de início inválida deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>startDate=invalid</t>
+  </si>
+  <si>
+    <t>TI-17</t>
+  </si>
+  <si>
+    <t>RN: duração esperada inválida deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>expectedDuration=0</t>
+  </si>
+  <si>
+    <t>TI-18</t>
+  </si>
+  <si>
+    <t>RN: status do lote inválido deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>status=desconhecido</t>
+  </si>
+  <si>
+    <t>TI-19</t>
+  </si>
+  <si>
+    <t>RF: criar tarefa válida</t>
+  </si>
+  <si>
+    <t>POST /tasks</t>
+  </si>
+  <si>
+    <t>Tarefa com dados válidos</t>
+  </si>
+  <si>
+    <t>TI-20</t>
+  </si>
+  <si>
+    <t>RN: título da tarefa é obrigatório</t>
+  </si>
+  <si>
+    <t>title=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-21</t>
+  </si>
+  <si>
+    <t>RN: batchId é obrigatório</t>
+  </si>
+  <si>
+    <t>batchId=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-22</t>
+  </si>
+  <si>
+    <t>RN: data de conclusão inválida deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>dueDate=invalid</t>
+  </si>
+  <si>
+    <t>TI-23</t>
+  </si>
+  <si>
+    <t>RN: status da tarefa inválido deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>status=invalido</t>
+  </si>
+  <si>
+    <t>TI-24</t>
+  </si>
+  <si>
+    <t>RF: registar medição válida</t>
+  </si>
+  <si>
+    <t>POST /measurements</t>
+  </si>
+  <si>
+    <t>Medição com dados válidos</t>
+  </si>
+  <si>
+    <t>TI-25</t>
+  </si>
+  <si>
+    <t>RN: sensorId é obrigatório</t>
+  </si>
+  <si>
+    <t>sensorId=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-26</t>
+  </si>
+  <si>
+    <t>RN: valor da medição deve ser numérico</t>
+  </si>
+  <si>
+    <t>value=não-numérico</t>
+  </si>
+  <si>
+    <t>TI-27</t>
+  </si>
+  <si>
+    <t>RN: timestamp inválido deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>timestamp=invalid</t>
+  </si>
+  <si>
+    <t>TI-28</t>
+  </si>
+  <si>
+    <t>RN: classificar alerta como Normal</t>
+  </si>
+  <si>
+    <t>POST /alerts</t>
+  </si>
+  <si>
+    <t>200 OK com severity Normal</t>
+  </si>
+  <si>
+    <t>Valores nominais</t>
+  </si>
+  <si>
+    <t>TI-29</t>
+  </si>
+  <si>
+    <t>RN: classificar alerta como Aviso</t>
+  </si>
+  <si>
+    <t>200 OK com severity Aviso</t>
+  </si>
+  <si>
+    <t>Temp &gt; limite</t>
+  </si>
+  <si>
+    <t>TI-30</t>
+  </si>
+  <si>
+    <t>RN: classificar alerta como Crítico (temperatura)</t>
+  </si>
+  <si>
+    <t>200 OK com severity Crítico</t>
+  </si>
+  <si>
+    <t>TI-31</t>
+  </si>
+  <si>
+    <t>RN: classificar alerta como Crítico (humidade)</t>
+  </si>
+  <si>
+    <t>Hum &lt; minH - 5</t>
+  </si>
+  <si>
+    <t>TI-32</t>
+  </si>
+  <si>
+    <t>RN: alerta Informativo quando sensor com erro</t>
+  </si>
+  <si>
+    <t>200 OK com severity Informativo</t>
+  </si>
+  <si>
+    <t>sensorOK=false</t>
+  </si>
+  <si>
+    <t>TI-33</t>
+  </si>
+  <si>
+    <t>RN: limites são obrigatórios</t>
+  </si>
+  <si>
+    <t>limits=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-34</t>
+  </si>
+  <si>
+    <t>RF: criar regra de automação válida</t>
+  </si>
+  <si>
+    <t>POST /automation</t>
+  </si>
+  <si>
+    <t>Regra com trigger e action</t>
+  </si>
+  <si>
+    <t>TI-35</t>
+  </si>
+  <si>
+    <t>RN: trigger é obrigatório</t>
+  </si>
+  <si>
+    <t>trigger=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-36</t>
+  </si>
+  <si>
+    <t>RN: action é obrigatório</t>
+  </si>
+  <si>
+    <t>action=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-37</t>
+  </si>
+  <si>
+    <t>RN: enabled deve ser booleano</t>
+  </si>
+  <si>
+    <t>enabled=string</t>
+  </si>
+  <si>
+    <t>TI-38</t>
+  </si>
+  <si>
+    <t>RF: gerar relatório válido</t>
+  </si>
+  <si>
+    <t>POST /reports</t>
+  </si>
+  <si>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t>Tipo=weekly, datas válidas</t>
+  </si>
+  <si>
+    <t>TI-39</t>
+  </si>
+  <si>
+    <t>RN: tipo de relatório inválido deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>type=yearly</t>
+  </si>
+  <si>
+    <t>TI-40</t>
+  </si>
+  <si>
+    <t>RN: data inicial inválida deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>from=invalid</t>
+  </si>
+  <si>
+    <t>TI-41</t>
+  </si>
+  <si>
+    <t>RN: data final inválida deve ser rejeitada</t>
+  </si>
+  <si>
+    <t>to=invalid</t>
+  </si>
+  <si>
+    <t>TI-42</t>
+  </si>
+  <si>
+    <t>RN: intervalo de datas inválido deve ser rejeitado</t>
+  </si>
+  <si>
+    <t>from &gt; to</t>
+  </si>
+  <si>
+    <t>TI-43</t>
+  </si>
+  <si>
+    <t>RF: registar entrada de auditoria válida</t>
+  </si>
+  <si>
+    <t>POST /audit</t>
+  </si>
+  <si>
+    <t>Auditoria com dados válidos</t>
+  </si>
+  <si>
+    <t>TI-44</t>
+  </si>
+  <si>
+    <t>RN: userId é obrigatório</t>
+  </si>
+  <si>
+    <t>userId=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-45</t>
+  </si>
+  <si>
+    <t>RN: evento é obrigatório</t>
+  </si>
+  <si>
+    <t>event=[vazio]</t>
+  </si>
+  <si>
+    <t>TI-46</t>
+  </si>
+  <si>
+    <t>Novos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,11 +1208,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
     <font>
       <u/>
@@ -921,12 +1230,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -941,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -949,52 +1264,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
@@ -1002,7 +1316,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1018,16 +1332,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}" name="Tabela1" displayName="Tabela1" ref="B3:H64" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B3:H64" xr:uid="{76165D67-EC10-4749-869D-85748592F61E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H104" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B3:H104" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5FFE78D4-90B0-4698-A26D-BEF2D31F1891}" name="ID" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{FC908435-E6B2-49F9-9C0A-FD430037704E}" name="Requisito / Regra" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{5C08DE87-FCE6-4A45-82A4-D3524E99CF6D}" name="Endpoint" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DE5E5E5D-1555-4BF1-A284-835BF06145E9}" name="Nível" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{91A14162-1739-4C59-BD55-0360A1D95F92}" name="Técnica" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{DB9FA437-A651-41FB-8B38-9B247A465023}" name="Resultado Esperado" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{6265D475-AE32-412A-A1EC-55923B62F369}" name="Pré-condições" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requisito / Regra" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Endpoint" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nível" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Técnica" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Resultado Esperado" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pré-condições" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1349,21 +1663,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E031847A-75C8-407F-B2D5-2072BA2EA35A}">
-  <dimension ref="B2:R64"/>
-  <sheetFormatPr defaultColWidth="8.15234375" defaultRowHeight="27" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:R104"/>
+  <sheetFormatPr defaultColWidth="8.140625" defaultRowHeight="27" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="10.53515625" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="21.84375" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="22.84375" customWidth="1"/>
-    <col min="7" max="7" width="27.84375" customWidth="1"/>
-    <col min="8" max="8" width="20.69140625" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.85546875" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="36.75" customHeight="1"/>
-    <row r="3" spans="2:18" ht="14.6">
+    <row r="3" spans="2:18" ht="14.65" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1701,7 @@
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="2:18" ht="43.75">
+    <row r="4" spans="2:18" ht="43.7" customHeight="1">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1410,7 +1724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="43.75">
+    <row r="5" spans="2:18" ht="43.7" customHeight="1">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1434,7 +1748,7 @@
       </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="2:18" ht="43.75">
+    <row r="6" spans="2:18" ht="43.7" customHeight="1">
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1457,7 +1771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="29.15">
+    <row r="7" spans="2:18" ht="29.1" customHeight="1">
       <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
@@ -1480,7 +1794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="43.75">
+    <row r="8" spans="2:18" ht="43.7" customHeight="1">
       <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1503,7 +1817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="29.15">
+    <row r="9" spans="2:18" ht="29.1" customHeight="1">
       <c r="B9" s="2" t="s">
         <v>31</v>
       </c>
@@ -1526,7 +1840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="43.75">
+    <row r="10" spans="2:18" ht="43.7" customHeight="1">
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
@@ -1549,7 +1863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="43.75">
+    <row r="11" spans="2:18" ht="43.7" customHeight="1">
       <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
@@ -1573,7 +1887,7 @@
       </c>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="2:18" ht="43.75">
+    <row r="12" spans="2:18" ht="43.7" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
@@ -1596,7 +1910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="43.75">
+    <row r="13" spans="2:18" ht="43.7" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>44</v>
       </c>
@@ -1626,7 +1940,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="2:18" ht="29.15">
+    <row r="14" spans="2:18" ht="29.1" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -1656,7 +1970,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="2:18" ht="43.75">
+    <row r="15" spans="2:18" ht="43.7" customHeight="1">
       <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
@@ -1686,7 +2000,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="2:18" ht="43.75">
+    <row r="16" spans="2:18" ht="43.7" customHeight="1">
       <c r="B16" s="2" t="s">
         <v>60</v>
       </c>
@@ -1716,7 +2030,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="2:18" ht="29.15">
+    <row r="17" spans="2:18" ht="29.1" customHeight="1">
       <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
@@ -1746,7 +2060,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="2:18" ht="43.75">
+    <row r="18" spans="2:18" ht="43.7" customHeight="1">
       <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
@@ -1776,7 +2090,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="2:18" ht="29.15">
+    <row r="19" spans="2:18" ht="29.1" customHeight="1">
       <c r="B19" s="2" t="s">
         <v>73</v>
       </c>
@@ -1806,7 +2120,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="2:18" ht="29.15">
+    <row r="20" spans="2:18" ht="29.1" customHeight="1">
       <c r="B20" s="2" t="s">
         <v>79</v>
       </c>
@@ -1836,7 +2150,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="2:18" ht="29.15">
+    <row r="21" spans="2:18" ht="29.1" customHeight="1">
       <c r="B21" s="2" t="s">
         <v>83</v>
       </c>
@@ -1866,7 +2180,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="2:18" ht="43.75">
+    <row r="22" spans="2:18" ht="43.7" customHeight="1">
       <c r="B22" s="2" t="s">
         <v>88</v>
       </c>
@@ -1896,7 +2210,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="2:18" ht="29.15">
+    <row r="23" spans="2:18" ht="29.1" customHeight="1">
       <c r="B23" s="2" t="s">
         <v>93</v>
       </c>
@@ -1926,7 +2240,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="2:18" ht="43.75">
+    <row r="24" spans="2:18" ht="43.7" customHeight="1">
       <c r="B24" s="2" t="s">
         <v>97</v>
       </c>
@@ -1956,7 +2270,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="2:18" ht="29.15">
+    <row r="25" spans="2:18" ht="29.1" customHeight="1">
       <c r="B25" s="2" t="s">
         <v>101</v>
       </c>
@@ -1986,7 +2300,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="2:18" ht="29.15">
+    <row r="26" spans="2:18" ht="29.1" customHeight="1">
       <c r="B26" s="2" t="s">
         <v>105</v>
       </c>
@@ -2016,7 +2330,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="2:18" ht="29.15">
+    <row r="27" spans="2:18" ht="29.1" customHeight="1">
       <c r="B27" s="2" t="s">
         <v>110</v>
       </c>
@@ -2046,7 +2360,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="2:18" ht="29.15">
+    <row r="28" spans="2:18" ht="29.1" customHeight="1">
       <c r="B28" s="2" t="s">
         <v>114</v>
       </c>
@@ -2076,7 +2390,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="2:18" ht="29.15">
+    <row r="29" spans="2:18" ht="29.1" customHeight="1">
       <c r="B29" s="2" t="s">
         <v>118</v>
       </c>
@@ -2106,7 +2420,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="2:18" ht="29.15">
+    <row r="30" spans="2:18" ht="29.1" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>122</v>
       </c>
@@ -2136,7 +2450,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="2:18" ht="43.75">
+    <row r="31" spans="2:18" ht="43.7" customHeight="1">
       <c r="B31" s="2" t="s">
         <v>126</v>
       </c>
@@ -2166,7 +2480,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="2:18" ht="43.75">
+    <row r="32" spans="2:18" ht="43.7" customHeight="1">
       <c r="B32" s="2" t="s">
         <v>131</v>
       </c>
@@ -2196,7 +2510,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="2:18" ht="29.15">
+    <row r="33" spans="2:18" ht="29.1" customHeight="1">
       <c r="B33" s="2" t="s">
         <v>135</v>
       </c>
@@ -2226,7 +2540,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="2:18" ht="43.75">
+    <row r="34" spans="2:18" ht="43.7" customHeight="1">
       <c r="B34" s="2" t="s">
         <v>139</v>
       </c>
@@ -2256,7 +2570,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="2:18" ht="43.75">
+    <row r="35" spans="2:18" ht="43.7" customHeight="1">
       <c r="B35" s="2" t="s">
         <v>143</v>
       </c>
@@ -2286,7 +2600,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="2:18" ht="29.15">
+    <row r="36" spans="2:18" ht="29.1" customHeight="1">
       <c r="B36" s="2" t="s">
         <v>147</v>
       </c>
@@ -2316,7 +2630,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="2:18" ht="43.75">
+    <row r="37" spans="2:18" ht="43.7" customHeight="1">
       <c r="B37" s="2" t="s">
         <v>152</v>
       </c>
@@ -2346,7 +2660,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="2:18" ht="29.15">
+    <row r="38" spans="2:18" ht="29.1" customHeight="1">
       <c r="B38" s="2" t="s">
         <v>155</v>
       </c>
@@ -2376,7 +2690,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="2:18" ht="29.15">
+    <row r="39" spans="2:18" ht="29.1" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>159</v>
       </c>
@@ -2406,7 +2720,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="2:18" ht="29.15">
+    <row r="40" spans="2:18" ht="29.1" customHeight="1">
       <c r="B40" s="2" t="s">
         <v>164</v>
       </c>
@@ -2436,7 +2750,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="2:18" ht="29.15">
+    <row r="41" spans="2:18" ht="29.1" customHeight="1">
       <c r="B41" s="2" t="s">
         <v>167</v>
       </c>
@@ -2466,7 +2780,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="2:18" ht="29.15">
+    <row r="42" spans="2:18" ht="29.1" customHeight="1">
       <c r="B42" s="2" t="s">
         <v>172</v>
       </c>
@@ -2496,7 +2810,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="2:18" ht="29.15">
+    <row r="43" spans="2:18" ht="29.1" customHeight="1">
       <c r="B43" s="2" t="s">
         <v>176</v>
       </c>
@@ -2526,7 +2840,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="2:18" ht="29.15">
+    <row r="44" spans="2:18" ht="29.1" customHeight="1">
       <c r="B44" s="2" t="s">
         <v>180</v>
       </c>
@@ -2556,7 +2870,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="2:18" ht="29.15">
+    <row r="45" spans="2:18" ht="29.1" customHeight="1">
       <c r="B45" s="2" t="s">
         <v>184</v>
       </c>
@@ -2579,7 +2893,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="46" spans="2:18" ht="43.75">
+    <row r="46" spans="2:18" ht="43.7" customHeight="1">
       <c r="B46" s="2" t="s">
         <v>188</v>
       </c>
@@ -2602,7 +2916,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="29.15">
+    <row r="47" spans="2:18" ht="29.1" customHeight="1">
       <c r="B47" s="2" t="s">
         <v>191</v>
       </c>
@@ -2625,7 +2939,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="2:18" ht="43.75">
+    <row r="48" spans="2:18" ht="43.7" customHeight="1">
       <c r="B48" s="2" t="s">
         <v>193</v>
       </c>
@@ -3016,11 +3330,934 @@
         <v>258</v>
       </c>
     </row>
+    <row r="65" spans="2:10" ht="30">
+      <c r="B65" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="45">
+      <c r="B66" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="45">
+      <c r="B67" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="45">
+      <c r="B68" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="45">
+      <c r="B69" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="45">
+      <c r="B70" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="30">
+      <c r="B71" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="30">
+      <c r="B72" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="30">
+      <c r="B73" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="45">
+      <c r="B74" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="45">
+      <c r="B75" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="45">
+      <c r="B76" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="30">
+      <c r="B77" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="30">
+      <c r="B78" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="30">
+      <c r="B79" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="45">
+      <c r="B80" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" ht="45">
+      <c r="B81" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" ht="30">
+      <c r="B82" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" ht="30">
+      <c r="B83" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" ht="30">
+      <c r="B84" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="30">
+      <c r="B85" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="30">
+      <c r="B86" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" ht="30">
+      <c r="B87" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" ht="45">
+      <c r="B88" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" ht="45">
+      <c r="B89" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" ht="30">
+      <c r="B90" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" ht="30">
+      <c r="B91" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" ht="30">
+      <c r="B92" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" ht="15">
+      <c r="B93" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" ht="15">
+      <c r="B94" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="30">
+      <c r="B95" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" ht="30">
+      <c r="B96" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" ht="45">
+      <c r="B97" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" ht="30">
+      <c r="B98" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" ht="30">
+      <c r="B99" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" ht="45">
+      <c r="B100" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" ht="30">
+      <c r="B101" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" ht="15">
+      <c r="B102" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="15">
+      <c r="B103" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="30">
+      <c r="B104" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/GreenHerb/Matriz de rastreabilidade.xlsx
+++ b/GreenHerb/Matriz de rastreabilidade.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\Engenharia-Software-II\GreenHerb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922F8FF2-DAB3-4885-A25D-A04B8EEEFB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C8CCE-D7C0-4DEA-98CD-3DACF926493B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="434">
   <si>
     <t>ID</t>
   </si>
@@ -1187,6 +1187,141 @@
   </si>
   <si>
     <t>Novos</t>
+  </si>
+  <si>
+    <t>TS-01</t>
+  </si>
+  <si>
+    <t>Múltiplos</t>
+  </si>
+  <si>
+    <t>Sistema</t>
+  </si>
+  <si>
+    <t>Teste de Percurso</t>
+  </si>
+  <si>
+    <t>Registo de medição -&gt; Geração de Alerta -&gt; Consulta no Dashboard</t>
+  </si>
+  <si>
+    <t>Sensor ativo e lote em curso</t>
+  </si>
+  <si>
+    <t>TS-02</t>
+  </si>
+  <si>
+    <t>Transição de Estados</t>
+  </si>
+  <si>
+    <t>Alerta Crítico -&gt; Criação de Plano de Emergência -&gt; Resolução com Justificação</t>
+  </si>
+  <si>
+    <t>Alerta crítico ativo</t>
+  </si>
+  <si>
+    <t>TS-03</t>
+  </si>
+  <si>
+    <t>Ações de diferentes utilizadores (Admin/Técnico) aparecem listadas no Log de Auditoria</t>
+  </si>
+  <si>
+    <t>Sessões ativas</t>
+  </si>
+  <si>
+    <t>TS-04</t>
+  </si>
+  <si>
+    <t>Lote concluído -&gt; Cálculo de produtividade -&gt; PDF/JSON de relatório gerado</t>
+  </si>
+  <si>
+    <t>Lote com medições históricas</t>
+  </si>
+  <si>
+    <t>TU-55</t>
+  </si>
+  <si>
+    <t>calculateProd()</t>
+  </si>
+  <si>
+    <t>Retorno de 100% se colheita = planeado</t>
+  </si>
+  <si>
+    <t>Lote concluído</t>
+  </si>
+  <si>
+    <t>TU-56</t>
+  </si>
+  <si>
+    <t>calculateLoss()</t>
+  </si>
+  <si>
+    <t>Se colheita &gt; planeado, perda deve ser 0</t>
+  </si>
+  <si>
+    <t>Dados de colheita inseridos</t>
+  </si>
+  <si>
+    <t>TU-57</t>
+  </si>
+  <si>
+    <t>updateBatch()</t>
+  </si>
+  <si>
+    <t>Erro ao tentar mudar nome/datas de um lote já "concluído"</t>
+  </si>
+  <si>
+    <t>Lote em estado 'concluído'</t>
+  </si>
+  <si>
+    <t>TU-58</t>
+  </si>
+  <si>
+    <t>Se sensorOK=false, ignora limites e retorna "Informativo"</t>
+  </si>
+  <si>
+    <t>Sensor em falha</t>
+  </si>
+  <si>
+    <t>TU-59</t>
+  </si>
+  <si>
+    <t>runAutomation()</t>
+  </si>
+  <si>
+    <t>Caixa-Branca</t>
+  </si>
+  <si>
+    <t>Retorna "Ação sugerida" e não executa o atuador</t>
+  </si>
+  <si>
+    <t>Estufa em Modo Manual</t>
+  </si>
+  <si>
+    <t>RF-07: Fluxo de monitorização completo</t>
+  </si>
+  <si>
+    <t>RN-05: Ciclo de vida de resolução de incidentes</t>
+  </si>
+  <si>
+    <t>RN-09: Rastreabilidade Total (Auditoria)</t>
+  </si>
+  <si>
+    <t>RF-08: Geração de Relatório de fecho de lote</t>
+  </si>
+  <si>
+    <t>RN-XX: Cálculo de Produtividade</t>
+  </si>
+  <si>
+    <t>RN-XX: Cálculo de Perdas</t>
+  </si>
+  <si>
+    <t>RN-08: Bloqueio de alteração em Lote Concluído</t>
+  </si>
+  <si>
+    <t>RN-02: Prioridade de Alerta (Informativo &gt; Outros)</t>
+  </si>
+  <si>
+    <t>RN-10: Execução de Automação em Modo Manual</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1272,6 +1407,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1332,8 +1470,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H104" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B3:H104" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H113" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B3:H113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requisito / Regra" dataDxfId="5"/>
@@ -1664,16 +1802,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:R104"/>
-  <sheetFormatPr defaultColWidth="8.140625" defaultRowHeight="27" customHeight="1"/>
+  <dimension ref="B2:R113"/>
+  <sheetFormatPr defaultColWidth="8.1328125" defaultRowHeight="27" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.59765625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.86328125" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" customWidth="1"/>
-    <col min="7" max="7" width="27.85546875" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.86328125" customWidth="1"/>
+    <col min="7" max="7" width="27.86328125" customWidth="1"/>
+    <col min="8" max="8" width="20.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="36.75" customHeight="1"/>
@@ -3330,7 +3468,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="2:10" ht="30">
+    <row r="65" spans="2:10" ht="28.5">
       <c r="B65" s="2" t="s">
         <v>259</v>
       </c>
@@ -3356,7 +3494,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="66" spans="2:10" ht="45">
+    <row r="66" spans="2:10" ht="28.5">
       <c r="B66" s="2" t="s">
         <v>263</v>
       </c>
@@ -3379,7 +3517,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="67" spans="2:10" ht="45">
+    <row r="67" spans="2:10" ht="28.5">
       <c r="B67" s="2" t="s">
         <v>266</v>
       </c>
@@ -3402,7 +3540,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="68" spans="2:10" ht="45">
+    <row r="68" spans="2:10" ht="28.5">
       <c r="B68" s="2" t="s">
         <v>269</v>
       </c>
@@ -3425,7 +3563,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="69" spans="2:10" ht="45">
+    <row r="69" spans="2:10" ht="42.75">
       <c r="B69" s="2" t="s">
         <v>272</v>
       </c>
@@ -3448,7 +3586,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="70" spans="2:10" ht="45">
+    <row r="70" spans="2:10" ht="28.5">
       <c r="B70" s="2" t="s">
         <v>275</v>
       </c>
@@ -3471,7 +3609,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="71" spans="2:10" ht="30">
+    <row r="71" spans="2:10" ht="28.5">
       <c r="B71" s="2" t="s">
         <v>278</v>
       </c>
@@ -3494,7 +3632,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="72" spans="2:10" ht="30">
+    <row r="72" spans="2:10" ht="14.25">
       <c r="B72" s="2" t="s">
         <v>280</v>
       </c>
@@ -3517,7 +3655,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="73" spans="2:10" ht="30">
+    <row r="73" spans="2:10" ht="28.5">
       <c r="B73" s="2" t="s">
         <v>284</v>
       </c>
@@ -3540,7 +3678,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="74" spans="2:10" ht="45">
+    <row r="74" spans="2:10" ht="28.5">
       <c r="B74" s="2" t="s">
         <v>287</v>
       </c>
@@ -3563,7 +3701,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="75" spans="2:10" ht="45">
+    <row r="75" spans="2:10" ht="28.5">
       <c r="B75" s="2" t="s">
         <v>290</v>
       </c>
@@ -3586,7 +3724,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="76" spans="2:10" ht="45">
+    <row r="76" spans="2:10" ht="28.5">
       <c r="B76" s="2" t="s">
         <v>293</v>
       </c>
@@ -3609,7 +3747,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="77" spans="2:10" ht="30">
+    <row r="77" spans="2:10" ht="14.25">
       <c r="B77" s="2" t="s">
         <v>296</v>
       </c>
@@ -3632,7 +3770,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="78" spans="2:10" ht="30">
+    <row r="78" spans="2:10" ht="28.5">
       <c r="B78" s="2" t="s">
         <v>300</v>
       </c>
@@ -3655,7 +3793,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="79" spans="2:10" ht="30">
+    <row r="79" spans="2:10" ht="14.25">
       <c r="B79" s="2" t="s">
         <v>303</v>
       </c>
@@ -3678,7 +3816,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="80" spans="2:10" ht="45">
+    <row r="80" spans="2:10" ht="28.5">
       <c r="B80" s="2" t="s">
         <v>306</v>
       </c>
@@ -3701,7 +3839,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="45">
+    <row r="81" spans="2:8" ht="28.5">
       <c r="B81" s="2" t="s">
         <v>309</v>
       </c>
@@ -3724,7 +3862,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="30">
+    <row r="82" spans="2:8" ht="28.5">
       <c r="B82" s="2" t="s">
         <v>312</v>
       </c>
@@ -3747,7 +3885,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="30">
+    <row r="83" spans="2:8" ht="14.25">
       <c r="B83" s="2" t="s">
         <v>316</v>
       </c>
@@ -3770,7 +3908,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="30">
+    <row r="84" spans="2:8" ht="28.5">
       <c r="B84" s="2" t="s">
         <v>319</v>
       </c>
@@ -3793,7 +3931,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="30">
+    <row r="85" spans="2:8" ht="28.5">
       <c r="B85" s="2" t="s">
         <v>322</v>
       </c>
@@ -3816,7 +3954,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="30">
+    <row r="86" spans="2:8" ht="28.5">
       <c r="B86" s="2" t="s">
         <v>325</v>
       </c>
@@ -3839,7 +3977,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="30">
+    <row r="87" spans="2:8" ht="28.5">
       <c r="B87" s="2" t="s">
         <v>330</v>
       </c>
@@ -3862,7 +4000,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="45">
+    <row r="88" spans="2:8" ht="28.5">
       <c r="B88" s="2" t="s">
         <v>334</v>
       </c>
@@ -3885,7 +4023,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="45">
+    <row r="89" spans="2:8" ht="28.5">
       <c r="B89" s="2" t="s">
         <v>337</v>
       </c>
@@ -3908,7 +4046,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="30">
+    <row r="90" spans="2:8" ht="28.5">
       <c r="B90" s="2" t="s">
         <v>340</v>
       </c>
@@ -3931,7 +4069,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="30">
+    <row r="91" spans="2:8" ht="14.25">
       <c r="B91" s="2" t="s">
         <v>344</v>
       </c>
@@ -3954,7 +4092,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="30">
+    <row r="92" spans="2:8" ht="28.5">
       <c r="B92" s="2" t="s">
         <v>347</v>
       </c>
@@ -3977,7 +4115,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="15">
+    <row r="93" spans="2:8" ht="14.25">
       <c r="B93" s="2" t="s">
         <v>351</v>
       </c>
@@ -4000,7 +4138,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="15">
+    <row r="94" spans="2:8" ht="14.25">
       <c r="B94" s="2" t="s">
         <v>354</v>
       </c>
@@ -4023,7 +4161,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="30">
+    <row r="95" spans="2:8" ht="28.5">
       <c r="B95" s="2" t="s">
         <v>357</v>
       </c>
@@ -4046,7 +4184,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="30">
+    <row r="96" spans="2:8" ht="28.5">
       <c r="B96" s="2" t="s">
         <v>360</v>
       </c>
@@ -4069,7 +4207,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="45">
+    <row r="97" spans="2:8" ht="28.5">
       <c r="B97" s="2" t="s">
         <v>365</v>
       </c>
@@ -4092,7 +4230,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="98" spans="2:8" ht="30">
+    <row r="98" spans="2:8" ht="28.5">
       <c r="B98" s="2" t="s">
         <v>368</v>
       </c>
@@ -4115,7 +4253,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="30">
+    <row r="99" spans="2:8" ht="28.5">
       <c r="B99" s="2" t="s">
         <v>371</v>
       </c>
@@ -4138,7 +4276,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="45">
+    <row r="100" spans="2:8" ht="28.5">
       <c r="B100" s="2" t="s">
         <v>374</v>
       </c>
@@ -4161,7 +4299,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="30">
+    <row r="101" spans="2:8" ht="28.5">
       <c r="B101" s="2" t="s">
         <v>377</v>
       </c>
@@ -4184,7 +4322,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="102" spans="2:8" ht="15">
+    <row r="102" spans="2:8" ht="14.25">
       <c r="B102" s="2" t="s">
         <v>381</v>
       </c>
@@ -4207,7 +4345,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="15">
+    <row r="103" spans="2:8" ht="14.25">
       <c r="B103" s="2" t="s">
         <v>384</v>
       </c>
@@ -4230,7 +4368,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="30">
+    <row r="104" spans="2:8" ht="28.5">
       <c r="B104" s="2" t="s">
         <v>387</v>
       </c>
@@ -4253,11 +4391,218 @@
         <v>324</v>
       </c>
     </row>
+    <row r="105" spans="2:8" ht="27" customHeight="1">
+      <c r="B105" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" ht="27" customHeight="1">
+      <c r="B106" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" ht="27" customHeight="1">
+      <c r="B107" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" ht="27" customHeight="1">
+      <c r="B108" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" ht="27" customHeight="1">
+      <c r="B109" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" ht="27" customHeight="1">
+      <c r="B110" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" ht="27" customHeight="1">
+      <c r="B111" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" ht="27" customHeight="1">
+      <c r="B112" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" ht="27" customHeight="1">
+      <c r="B113" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/GreenHerb/Matriz de rastreabilidade.xlsx
+++ b/GreenHerb/Matriz de rastreabilidade.xlsx
@@ -5,22 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Escola\ES2\GreenHerb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\GreenHerb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D45379C-BA5D-4011-A6DF-60D5BCDF7863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E88105C-86B8-401B-934B-8A57215A0698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Testes" sheetId="1" r:id="rId1"/>
+    <sheet name="Documentação White Box" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="1194">
   <si>
     <t>ID</t>
   </si>
@@ -3188,13 +3189,1599 @@
   </si>
   <si>
     <t>Particionamento de Equivalência (perfil Responsável)</t>
+  </si>
+  <si>
+    <t>ID do Caso de Teste</t>
+  </si>
+  <si>
+    <t>TU-WB-04</t>
+  </si>
+  <si>
+    <t>TU-WB-05</t>
+  </si>
+  <si>
+    <t>TU-WB-06</t>
+  </si>
+  <si>
+    <t>TU-WB-07</t>
+  </si>
+  <si>
+    <t>TU-WB-08</t>
+  </si>
+  <si>
+    <t>TU-WB-01</t>
+  </si>
+  <si>
+    <t>TU-WB-02</t>
+  </si>
+  <si>
+    <t>TU-WB-03</t>
+  </si>
+  <si>
+    <t>ESTRUTURA A: Validação do Plano Pontual</t>
+  </si>
+  <si>
+    <r>
+      <t>Expressão Lógica Original:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if (plan.type === 'pontual' &amp;&amp; !plan.authorizedByResponsible)</t>
+    </r>
+  </si>
+  <si>
+    <t>Condições Atómicas:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.type === 'pontual'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.authorizedByResponsible</t>
+    </r>
+  </si>
+  <si>
+    <t>Linha</t>
+  </si>
+  <si>
+    <t>C1​ (Pontual)</t>
+  </si>
+  <si>
+    <t>C2​ (Autorizado)</t>
+  </si>
+  <si>
+    <t>Resultado da Decisão</t>
+  </si>
+  <si>
+    <t>ID do Teste Associado</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Falso</t>
+  </si>
+  <si>
+    <r>
+      <t>Falso</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Não entra)</t>
+    </r>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>Verdadeiro</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <r>
+      <t>Verdadeiro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Entra no </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <r>
+      <t>Expressão Lógica Original:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if (plan.temperature &lt; 18 || plan.temperature &gt; 28)</t>
+    </r>
+  </si>
+  <si>
+    <t>C3: plan.temperature &lt; 18</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.temperature &gt; 28</t>
+    </r>
+  </si>
+  <si>
+    <t>C3​ (&lt;18)</t>
+  </si>
+  <si>
+    <t>C4​ (&gt;28)</t>
+  </si>
+  <si>
+    <t>Estado Prático</t>
+  </si>
+  <si>
+    <t>ID do Teste</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>Temperatura baixa (ex: 17)</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>Temperatura alta (ex: 29)</t>
+  </si>
+  <si>
+    <t>L7</t>
+  </si>
+  <si>
+    <t>Temperatura ideal (ex: 22)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ESTRUTURAS B1 : Parâmetros com Operador Composto </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+  </si>
+  <si>
+    <t>ESTRUTURA B2: Validação de Humidade</t>
+  </si>
+  <si>
+    <r>
+      <t>Expressão Lógica Original:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if (plan.humidity &lt; 40 || plan.humidity &gt; 80)</t>
+    </r>
+  </si>
+  <si>
+    <t>C5​ (&lt;40)</t>
+  </si>
+  <si>
+    <t>C6​ (&gt;80)</t>
+  </si>
+  <si>
+    <t>Valor de Teste Prático</t>
+  </si>
+  <si>
+    <t>L8</t>
+  </si>
+  <si>
+    <r>
+      <t>Verdadeiro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Dá erro)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Humidade = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>39</t>
+    </r>
+  </si>
+  <si>
+    <t>L9</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Humidade = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>81</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-09</t>
+  </si>
+  <si>
+    <t>L10</t>
+  </si>
+  <si>
+    <r>
+      <t>Falso</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Não dá erro)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Humidade = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C5: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.humidity &lt; 40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C6: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.humidity &gt; 80</t>
+    </r>
+  </si>
+  <si>
+    <t>ESTRUTURA B3: Validação de Luminosidade</t>
+  </si>
+  <si>
+    <r>
+      <t>Expressão Lógica Original:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if (plan.luminosity &lt; 5000 || plan.luminosity &gt; 25000)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C7: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.luminosity &lt; 5000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C8:: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.luminosity &gt; 25000</t>
+    </r>
+  </si>
+  <si>
+    <t>C7​ (&lt;5000)</t>
+  </si>
+  <si>
+    <t>C8​ (&gt;25000)</t>
+  </si>
+  <si>
+    <t>L11</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Luminosidade = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>4999</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-10</t>
+  </si>
+  <si>
+    <t>L12</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Luminosidade = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>25001</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-11</t>
+  </si>
+  <si>
+    <t>L13</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Luminosidade = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>15000</t>
+    </r>
+  </si>
+  <si>
+    <t>ESTRUTURA B4: Validação de Duração</t>
+  </si>
+  <si>
+    <r>
+      <t>Expressão Lógica Original:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if (plan.duration &lt; 1 || plan.duration &gt; 365)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C9: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.duration &lt; 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C10: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>plan.duration &gt; 365</t>
+    </r>
+  </si>
+  <si>
+    <t>C9​ (&lt;1)</t>
+  </si>
+  <si>
+    <t>C10​ (&gt;365)</t>
+  </si>
+  <si>
+    <t>L14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Duração = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-12</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Duração = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>366</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-13</t>
+  </si>
+  <si>
+    <t>L16</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Duração = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+  </si>
+  <si>
+    <t>validatePlan</t>
+  </si>
+  <si>
+    <t>Cobertura de Condições Múltiplas (Linha L1 / L7 / L10 / L13 / L16)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Objeto de plano com tipo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>'regular'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, autorização </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> e todos os parâmetros no centro dos intervalos ideais.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cobertura de Condições Múltiplas (Linha L2)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Objeto de plano com tipo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>'emergencia'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, autorização </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> e restantes parâmetros válidos.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cobertura de Condições Múltiplas (Linha L3)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Objeto de plano com tipo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>'pontual'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, autorização </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> e restantes parâmetros válidos.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cobertura de Condições Múltiplas (Linha L4)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Objeto de plano com tipo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>'pontual'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, autorização </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> e restantes parâmetros válidos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cobertura de Ramos / Decisões (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> simples)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Objeto de plano com tipo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>'invalido'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ou desconhecido. Parâmetros numéricos normais.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L5 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L6 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L8 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L9 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L11 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L12 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L14 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Condições Múltiplas (Linha L15 - operador </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cobertura de Caminhos (Path Coverage - múltiplos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ativos)</t>
+    </r>
+  </si>
+  <si>
+    <t>Objeto de plano enviado com todos os valores e limites corrompidos ao mesmo tempo.</t>
+  </si>
+  <si>
+    <t>RN-04: Tipo de plano regular e autorização.</t>
+  </si>
+  <si>
+    <r>
+      <t>Sucesso (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>). Array de erros vazio.</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-04: Tipo de plano e autorização facultativa.</t>
+  </si>
+  <si>
+    <t>RN-04: Bloqueio de plano pontual sem autorização.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Contém erro: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Plano pontual exige autorização"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-04: Desbloqueio de plano pontual com autorização.</t>
+  </si>
+  <si>
+    <t>RN-01: Lista de tipos válidos admitidos.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Contém erro: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Tipo de plano inválido"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo inferior de Temperatura.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Contém erro: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Temperatura fora do intervalo permitido"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>temperature</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 17 (abaixo do mínimo de 18).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo superior de Temperatura.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>temperature</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 29 (acima do máximo de 28).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo inferior de Humidade.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Contém erro: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Humidade fora do intervalo permitido"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>humidity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 39 (abaixo do mínimo de 40).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo superior de Humidade.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>humidity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 81 (acima do máximo de 80).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo inferior de Luminosidade.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Contém erro: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Luminosidade fora do intervalo permitido"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>luminosity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 4999 (abaixo do mínimo de 5000).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo superior de Luminosidade.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>luminosity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 25001 (acima do máximo de 25000).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo inferior de Duração.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Contém erro: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Duração fora do intervalo permitido"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>duration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 0 (abaixo do mínimo de 1).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02: Intervalo superior de Duração.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Parâmetro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>duration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> definido para 366 (acima do máximo de 365).</t>
+    </r>
+  </si>
+  <si>
+    <t>RN-02 / RN-04: Fluxo e acumulação de múltiplos erros.</t>
+  </si>
+  <si>
+    <r>
+      <t>Invalidação (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>). Devolve exatamente os 5 erros acumulados em simultâneo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sprint 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3244,8 +4831,60 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3267,6 +4906,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3322,7 +4967,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3375,6 +5020,34 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Neutral" xfId="3" xr:uid="{21D3CBB1-B351-413A-B518-A23BC59AF63F}"/>
@@ -3414,8 +5087,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H303" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B3:H303" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H317" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B3:H317" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requisito / Regra"/>
@@ -3746,8 +5419,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U303"/>
-  <sheetFormatPr defaultColWidth="8.140625" defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:U317"/>
+  <sheetFormatPr defaultColWidth="8.15234375" defaultRowHeight="27" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="3" width="50" customWidth="1"/>
@@ -3758,9 +5431,9 @@
     <col min="11" max="21" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:19" ht="14.6"/>
+    <row r="2" spans="2:19" ht="36.75" customHeight="1"/>
+    <row r="3" spans="2:19" ht="14.7" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -3784,7 +5457,7 @@
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" ht="43.75" customHeight="1">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3817,7 +5490,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" ht="43.75" customHeight="1">
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
@@ -3848,7 +5521,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" ht="43.75" customHeight="1">
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
@@ -3878,7 +5551,7 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="2:19" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" ht="29.15" customHeight="1">
       <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
@@ -3908,7 +5581,7 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" ht="43.75" customHeight="1">
       <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
@@ -3938,7 +5611,7 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="2:19" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:19" ht="29.15" customHeight="1">
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
@@ -3968,7 +5641,7 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:19" ht="43.75" customHeight="1">
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
@@ -3998,7 +5671,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:19" ht="43.75" customHeight="1">
       <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
@@ -4028,7 +5701,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:19" ht="43.75" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
@@ -4058,7 +5731,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:19" ht="43.75" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>41</v>
       </c>
@@ -4089,7 +5762,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="2:19" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:19" ht="29.15" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>44</v>
       </c>
@@ -4120,7 +5793,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:19" ht="43.75" customHeight="1">
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
@@ -4151,7 +5824,7 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="2:19" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" ht="43.75" customHeight="1">
       <c r="B16" s="2" t="s">
         <v>52</v>
       </c>
@@ -4182,7 +5855,7 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" ht="29.15" customHeight="1">
       <c r="B17" s="2" t="s">
         <v>54</v>
       </c>
@@ -4213,7 +5886,7 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" ht="43.75" customHeight="1">
       <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
@@ -4244,7 +5917,7 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" ht="29.15" customHeight="1">
       <c r="B19" s="2" t="s">
         <v>59</v>
       </c>
@@ -4275,7 +5948,7 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" ht="29.15" customHeight="1">
       <c r="B20" s="2" t="s">
         <v>62</v>
       </c>
@@ -4306,7 +5979,7 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" ht="29.15" customHeight="1">
       <c r="B21" s="2" t="s">
         <v>67</v>
       </c>
@@ -4337,7 +6010,7 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" ht="43.75" customHeight="1">
       <c r="B22" s="2" t="s">
         <v>71</v>
       </c>
@@ -4368,7 +6041,7 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" ht="29.15" customHeight="1">
       <c r="B23" s="2" t="s">
         <v>75</v>
       </c>
@@ -4402,7 +6075,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" ht="43.75" customHeight="1">
       <c r="B24" s="2" t="s">
         <v>82</v>
       </c>
@@ -4433,7 +6106,7 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" ht="29.15" customHeight="1">
       <c r="B25" s="2" t="s">
         <v>87</v>
       </c>
@@ -4464,7 +6137,7 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" ht="29.15" customHeight="1">
       <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
@@ -4497,7 +6170,7 @@
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" ht="29.15" customHeight="1">
       <c r="B27" s="2" t="s">
         <v>96</v>
       </c>
@@ -4530,7 +6203,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:21" ht="29.15" customHeight="1">
       <c r="B28" s="2" t="s">
         <v>100</v>
       </c>
@@ -4563,7 +6236,7 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:21" ht="29.15" customHeight="1">
       <c r="B29" s="2" t="s">
         <v>105</v>
       </c>
@@ -4596,7 +6269,7 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" ht="29.15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>110</v>
       </c>
@@ -4629,7 +6302,7 @@
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
     </row>
-    <row r="31" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" ht="43.75" customHeight="1">
       <c r="B31" s="2" t="s">
         <v>114</v>
       </c>
@@ -4662,7 +6335,7 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" ht="43.75" customHeight="1">
       <c r="B32" s="2" t="s">
         <v>118</v>
       </c>
@@ -4695,7 +6368,7 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
     </row>
-    <row r="33" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:21" ht="29.15" customHeight="1">
       <c r="B33" s="2" t="s">
         <v>122</v>
       </c>
@@ -4728,7 +6401,7 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" ht="43.75" customHeight="1">
       <c r="B34" s="2" t="s">
         <v>126</v>
       </c>
@@ -4761,7 +6434,7 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" ht="43.75" customHeight="1">
       <c r="B35" s="2" t="s">
         <v>130</v>
       </c>
@@ -4794,7 +6467,7 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" ht="29.15" customHeight="1">
       <c r="B36" s="2" t="s">
         <v>134</v>
       </c>
@@ -4826,7 +6499,7 @@
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
     </row>
-    <row r="37" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:21" ht="43.75" customHeight="1">
       <c r="B37" s="2" t="s">
         <v>138</v>
       </c>
@@ -4858,7 +6531,7 @@
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
     </row>
-    <row r="38" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" ht="29.15" customHeight="1">
       <c r="B38" s="2" t="s">
         <v>142</v>
       </c>
@@ -4890,7 +6563,7 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:21" ht="29.15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>146</v>
       </c>
@@ -4922,7 +6595,7 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:21" ht="29.15" customHeight="1">
       <c r="B40" s="2" t="s">
         <v>150</v>
       </c>
@@ -4947,7 +6620,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:21" ht="29.15" customHeight="1">
       <c r="B41" s="2" t="s">
         <v>154</v>
       </c>
@@ -4978,7 +6651,7 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:21" ht="29.15" customHeight="1">
       <c r="B42" s="2" t="s">
         <v>158</v>
       </c>
@@ -5009,7 +6682,7 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
     </row>
-    <row r="43" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:21" ht="29.15" customHeight="1">
       <c r="B43" s="2" t="s">
         <v>162</v>
       </c>
@@ -5040,7 +6713,7 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:21" ht="29.15" customHeight="1">
       <c r="B44" s="2" t="s">
         <v>166</v>
       </c>
@@ -5071,7 +6744,7 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
     </row>
-    <row r="45" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:21" ht="29.15" customHeight="1">
       <c r="B45" s="2" t="s">
         <v>170</v>
       </c>
@@ -5101,7 +6774,7 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
     </row>
-    <row r="46" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:21" ht="43.75" customHeight="1">
       <c r="B46" s="2" t="s">
         <v>176</v>
       </c>
@@ -5131,7 +6804,7 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47" spans="2:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:21" ht="29.15" customHeight="1">
       <c r="B47" s="2" t="s">
         <v>181</v>
       </c>
@@ -5161,7 +6834,7 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
     </row>
-    <row r="48" spans="2:21" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:21" ht="43.75" customHeight="1">
       <c r="B48" s="2" t="s">
         <v>186</v>
       </c>
@@ -5191,7 +6864,7 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="49" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:19" ht="27" customHeight="1">
       <c r="B49" s="2" t="s">
         <v>191</v>
       </c>
@@ -5221,7 +6894,7 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
     </row>
-    <row r="50" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:19" ht="27" customHeight="1">
       <c r="B50" s="2" t="s">
         <v>194</v>
       </c>
@@ -5251,7 +6924,7 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
     </row>
-    <row r="51" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:19" ht="27" customHeight="1">
       <c r="B51" s="2" t="s">
         <v>199</v>
       </c>
@@ -5281,7 +6954,7 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
     </row>
-    <row r="52" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:19" ht="27" customHeight="1">
       <c r="B52" s="2" t="s">
         <v>204</v>
       </c>
@@ -5311,7 +6984,7 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
     </row>
-    <row r="53" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:19" ht="27" customHeight="1">
       <c r="B53" s="2" t="s">
         <v>209</v>
       </c>
@@ -5341,7 +7014,7 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
     </row>
-    <row r="54" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:19" ht="27" customHeight="1">
       <c r="B54" s="2" t="s">
         <v>214</v>
       </c>
@@ -5371,7 +7044,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
     </row>
-    <row r="55" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:19" ht="27" customHeight="1">
       <c r="B55" s="2" t="s">
         <v>218</v>
       </c>
@@ -5401,7 +7074,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:19" ht="27" customHeight="1">
       <c r="B56" s="2" t="s">
         <v>224</v>
       </c>
@@ -5431,7 +7104,7 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
     </row>
-    <row r="57" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:19" ht="27" customHeight="1">
       <c r="B57" s="2" t="s">
         <v>228</v>
       </c>
@@ -5456,7 +7129,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:19" ht="27" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>232</v>
       </c>
@@ -5481,7 +7154,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:19" ht="27" customHeight="1">
       <c r="B59" s="2" t="s">
         <v>237</v>
       </c>
@@ -5506,7 +7179,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:19" ht="27" customHeight="1">
       <c r="B60" s="2" t="s">
         <v>242</v>
       </c>
@@ -5531,7 +7204,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:19" ht="27" customHeight="1">
       <c r="B61" s="2" t="s">
         <v>246</v>
       </c>
@@ -5556,7 +7229,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:19" ht="27" customHeight="1">
       <c r="B62" s="2" t="s">
         <v>248</v>
       </c>
@@ -5583,7 +7256,7 @@
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:19" ht="27" customHeight="1">
       <c r="B63" s="2" t="s">
         <v>250</v>
       </c>
@@ -5610,7 +7283,7 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:19" ht="27" customHeight="1">
       <c r="B64" s="2" t="s">
         <v>251</v>
       </c>
@@ -5637,7 +7310,7 @@
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
     </row>
-    <row r="65" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:14" ht="30" customHeight="1">
       <c r="B65" s="2" t="s">
         <v>252</v>
       </c>
@@ -5664,7 +7337,7 @@
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
     </row>
-    <row r="66" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14" ht="30" customHeight="1">
       <c r="B66" s="2" t="s">
         <v>253</v>
       </c>
@@ -5691,7 +7364,7 @@
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
     </row>
-    <row r="67" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:14" ht="30" customHeight="1">
       <c r="B67" s="2" t="s">
         <v>255</v>
       </c>
@@ -5718,7 +7391,7 @@
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:14" ht="30" customHeight="1">
       <c r="B68" s="2" t="s">
         <v>256</v>
       </c>
@@ -5745,7 +7418,7 @@
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:14" ht="30" customHeight="1">
       <c r="B69" s="2" t="s">
         <v>257</v>
       </c>
@@ -5772,7 +7445,7 @@
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
     </row>
-    <row r="70" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:14" ht="30" customHeight="1">
       <c r="B70" s="2" t="s">
         <v>258</v>
       </c>
@@ -5799,7 +7472,7 @@
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
     </row>
-    <row r="71" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:14" ht="30" customHeight="1">
       <c r="B71" s="2" t="s">
         <v>259</v>
       </c>
@@ -5826,7 +7499,7 @@
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14" ht="30" customHeight="1">
       <c r="B72" s="2" t="s">
         <v>261</v>
       </c>
@@ -5851,7 +7524,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:14" ht="30" customHeight="1">
       <c r="B73" s="2" t="s">
         <v>262</v>
       </c>
@@ -5876,7 +7549,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:14" ht="30" customHeight="1">
       <c r="B74" s="2" t="s">
         <v>263</v>
       </c>
@@ -5901,7 +7574,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:14" ht="30" customHeight="1">
       <c r="B75" s="2" t="s">
         <v>264</v>
       </c>
@@ -5926,7 +7599,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:14" ht="30" customHeight="1">
       <c r="B76" s="2" t="s">
         <v>265</v>
       </c>
@@ -5951,7 +7624,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:14" ht="30" customHeight="1">
       <c r="B77" s="2" t="s">
         <v>269</v>
       </c>
@@ -5976,7 +7649,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:14" ht="15" customHeight="1">
       <c r="B78" s="2" t="s">
         <v>272</v>
       </c>
@@ -6001,7 +7674,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:14" ht="30" customHeight="1">
       <c r="B79" s="2" t="s">
         <v>276</v>
       </c>
@@ -6026,7 +7699,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:14" ht="30" customHeight="1">
       <c r="B80" s="2" t="s">
         <v>279</v>
       </c>
@@ -6051,7 +7724,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:12" ht="30" customHeight="1">
       <c r="B81" s="2" t="s">
         <v>282</v>
       </c>
@@ -6076,7 +7749,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:12" ht="30" customHeight="1">
       <c r="B82" s="2" t="s">
         <v>286</v>
       </c>
@@ -6101,7 +7774,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:12" ht="45" customHeight="1">
       <c r="B83" s="5" t="s">
         <v>290</v>
       </c>
@@ -6127,7 +7800,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="84" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:12" ht="45" customHeight="1">
       <c r="B84" s="8" t="s">
         <v>297</v>
       </c>
@@ -6150,7 +7823,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="85" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:12" ht="45" customHeight="1">
       <c r="B85" s="5" t="s">
         <v>300</v>
       </c>
@@ -6173,7 +7846,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:12" ht="45" customHeight="1">
       <c r="B86" s="8" t="s">
         <v>303</v>
       </c>
@@ -6196,7 +7869,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="87" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:12" ht="45" customHeight="1">
       <c r="B87" s="5" t="s">
         <v>307</v>
       </c>
@@ -6219,7 +7892,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="88" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:12" ht="45" customHeight="1">
       <c r="B88" s="8" t="s">
         <v>312</v>
       </c>
@@ -6242,7 +7915,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="89" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:12" ht="45" customHeight="1">
       <c r="B89" s="5" t="s">
         <v>317</v>
       </c>
@@ -6265,7 +7938,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="90" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:12" ht="45" customHeight="1">
       <c r="B90" s="8" t="s">
         <v>320</v>
       </c>
@@ -6288,7 +7961,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="91" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:12" ht="45" customHeight="1">
       <c r="B91" s="5" t="s">
         <v>324</v>
       </c>
@@ -6311,7 +7984,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="92" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:12" ht="45" customHeight="1">
       <c r="B92" s="8" t="s">
         <v>329</v>
       </c>
@@ -6334,7 +8007,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:12" ht="45" customHeight="1">
       <c r="B93" s="5" t="s">
         <v>333</v>
       </c>
@@ -6357,7 +8030,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="94" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:12" ht="45" customHeight="1">
       <c r="B94" s="8" t="s">
         <v>337</v>
       </c>
@@ -6380,7 +8053,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="95" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:12" ht="45" customHeight="1">
       <c r="B95" s="5" t="s">
         <v>341</v>
       </c>
@@ -6403,7 +8076,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="96" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:12" ht="30" customHeight="1">
       <c r="B96" s="8" t="s">
         <v>346</v>
       </c>
@@ -6426,7 +8099,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" ht="30" customHeight="1">
       <c r="B97" s="5" t="s">
         <v>350</v>
       </c>
@@ -6449,7 +8122,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="98" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" ht="15" customHeight="1">
       <c r="B98" s="8" t="s">
         <v>352</v>
       </c>
@@ -6472,7 +8145,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" ht="30" customHeight="1">
       <c r="B99" s="5" t="s">
         <v>354</v>
       </c>
@@ -6495,7 +8168,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" ht="30" customHeight="1">
       <c r="B100" s="8" t="s">
         <v>356</v>
       </c>
@@ -6518,7 +8191,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" ht="45" customHeight="1">
       <c r="B101" s="5" t="s">
         <v>359</v>
       </c>
@@ -6541,7 +8214,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="102" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="45" customHeight="1">
       <c r="B102" s="8" t="s">
         <v>363</v>
       </c>
@@ -6564,7 +8237,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" ht="45" customHeight="1">
       <c r="B103" s="5" t="s">
         <v>368</v>
       </c>
@@ -6587,7 +8260,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" ht="30" customHeight="1">
       <c r="B104" s="8" t="s">
         <v>372</v>
       </c>
@@ -6610,7 +8283,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="105" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" ht="27" customHeight="1">
       <c r="B105" s="5" t="s">
         <v>376</v>
       </c>
@@ -6633,7 +8306,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" ht="27" customHeight="1">
       <c r="B106" s="8" t="s">
         <v>378</v>
       </c>
@@ -6656,7 +8329,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="107" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="27" customHeight="1">
       <c r="B107" s="5" t="s">
         <v>380</v>
       </c>
@@ -6679,7 +8352,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="108" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="27" customHeight="1">
       <c r="B108" s="8" t="s">
         <v>383</v>
       </c>
@@ -6702,7 +8375,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="27" customHeight="1">
       <c r="B109" s="5" t="s">
         <v>389</v>
       </c>
@@ -6725,7 +8398,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="27" customHeight="1">
       <c r="B110" s="8" t="s">
         <v>394</v>
       </c>
@@ -6748,7 +8421,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="111" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="27" customHeight="1">
       <c r="B111" s="5" t="s">
         <v>397</v>
       </c>
@@ -6771,7 +8444,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="112" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="27" customHeight="1">
       <c r="B112" s="8" t="s">
         <v>401</v>
       </c>
@@ -6794,7 +8467,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="113" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:8" ht="27" customHeight="1">
       <c r="B113" s="5" t="s">
         <v>405</v>
       </c>
@@ -6817,7 +8490,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="114" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:8" ht="27" customHeight="1">
       <c r="B114" s="8" t="s">
         <v>410</v>
       </c>
@@ -6840,7 +8513,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="115" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:8" ht="27" customHeight="1">
       <c r="B115" s="5" t="s">
         <v>413</v>
       </c>
@@ -6863,7 +8536,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="116" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:8" ht="27" customHeight="1">
       <c r="B116" s="8" t="s">
         <v>417</v>
       </c>
@@ -6886,7 +8559,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="117" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:8" ht="27" customHeight="1">
       <c r="B117" s="5" t="s">
         <v>422</v>
       </c>
@@ -6909,7 +8582,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="118" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:8" ht="27" customHeight="1">
       <c r="B118" s="8" t="s">
         <v>425</v>
       </c>
@@ -6932,7 +8605,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="119" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:8" ht="27" customHeight="1">
       <c r="B119" s="5" t="s">
         <v>429</v>
       </c>
@@ -6955,7 +8628,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="120" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:8" ht="27" customHeight="1">
       <c r="B120" s="8" t="s">
         <v>432</v>
       </c>
@@ -6978,7 +8651,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="121" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:8" ht="27" customHeight="1">
       <c r="B121" s="5" t="s">
         <v>436</v>
       </c>
@@ -7001,7 +8674,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="122" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:8" ht="27" customHeight="1">
       <c r="B122" s="8" t="s">
         <v>440</v>
       </c>
@@ -7024,7 +8697,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="123" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:8" ht="27" customHeight="1">
       <c r="B123" s="5" t="s">
         <v>445</v>
       </c>
@@ -7047,7 +8720,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:8" ht="27" customHeight="1">
       <c r="B124" s="8" t="s">
         <v>447</v>
       </c>
@@ -7070,7 +8743,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="125" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:8" ht="27" customHeight="1">
       <c r="B125" s="5" t="s">
         <v>451</v>
       </c>
@@ -7093,7 +8766,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="126" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:8" ht="27" customHeight="1">
       <c r="B126" s="8" t="s">
         <v>455</v>
       </c>
@@ -7116,7 +8789,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="127" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:8" ht="27" customHeight="1">
       <c r="B127" s="5" t="s">
         <v>459</v>
       </c>
@@ -7139,7 +8812,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="128" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:8" ht="27" customHeight="1">
       <c r="B128" s="8" t="s">
         <v>463</v>
       </c>
@@ -7162,7 +8835,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="129" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:8" ht="27" customHeight="1">
       <c r="B129" s="5" t="s">
         <v>465</v>
       </c>
@@ -7185,7 +8858,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="130" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" ht="27" customHeight="1">
       <c r="B130" s="8" t="s">
         <v>467</v>
       </c>
@@ -7208,7 +8881,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="131" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:8" ht="27" customHeight="1">
       <c r="B131" s="5" t="s">
         <v>470</v>
       </c>
@@ -7231,7 +8904,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="132" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:8" ht="27" customHeight="1">
       <c r="B132" s="8" t="s">
         <v>476</v>
       </c>
@@ -7254,7 +8927,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="133" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:8" ht="27" customHeight="1">
       <c r="B133" s="5" t="s">
         <v>481</v>
       </c>
@@ -7277,7 +8950,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="134" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:8" ht="27" customHeight="1">
       <c r="B134" s="8" t="s">
         <v>484</v>
       </c>
@@ -7300,7 +8973,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="135" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:8" ht="27" customHeight="1">
       <c r="B135" s="5" t="s">
         <v>488</v>
       </c>
@@ -7323,7 +8996,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="136" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:8" ht="27" customHeight="1">
       <c r="B136" s="8" t="s">
         <v>491</v>
       </c>
@@ -7346,7 +9019,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="137" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:8" ht="27" customHeight="1">
       <c r="B137" s="5" t="s">
         <v>494</v>
       </c>
@@ -7369,7 +9042,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="138" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:8" ht="27" customHeight="1">
       <c r="B138" s="8" t="s">
         <v>497</v>
       </c>
@@ -7392,7 +9065,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="139" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:8" ht="27" customHeight="1">
       <c r="B139" s="5" t="s">
         <v>501</v>
       </c>
@@ -7415,7 +9088,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="140" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:8" ht="27" customHeight="1">
       <c r="B140" s="8" t="s">
         <v>505</v>
       </c>
@@ -7438,7 +9111,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="141" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:8" ht="27" customHeight="1">
       <c r="B141" s="5" t="s">
         <v>509</v>
       </c>
@@ -7461,7 +9134,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="142" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:8" ht="27" customHeight="1">
       <c r="B142" s="8" t="s">
         <v>514</v>
       </c>
@@ -7484,7 +9157,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="143" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:8" ht="27" customHeight="1">
       <c r="B143" s="5" t="s">
         <v>518</v>
       </c>
@@ -7507,7 +9180,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="144" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:8" ht="27" customHeight="1">
       <c r="B144" s="8" t="s">
         <v>522</v>
       </c>
@@ -7530,7 +9203,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="145" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:8" ht="27" customHeight="1">
       <c r="B145" s="5" t="s">
         <v>527</v>
       </c>
@@ -7553,7 +9226,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="146" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:8" ht="27" customHeight="1">
       <c r="B146" s="8" t="s">
         <v>530</v>
       </c>
@@ -7576,7 +9249,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="147" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:8" ht="27" customHeight="1">
       <c r="B147" s="5" t="s">
         <v>534</v>
       </c>
@@ -7599,7 +9272,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="148" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:8" ht="27" customHeight="1">
       <c r="B148" s="8" t="s">
         <v>538</v>
       </c>
@@ -7622,7 +9295,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="149" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:8" ht="27" customHeight="1">
       <c r="B149" s="5" t="s">
         <v>543</v>
       </c>
@@ -7645,7 +9318,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="150" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:8" ht="27" customHeight="1">
       <c r="B150" s="8" t="s">
         <v>547</v>
       </c>
@@ -7668,7 +9341,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="151" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:8" ht="27" customHeight="1">
       <c r="B151" s="5" t="s">
         <v>551</v>
       </c>
@@ -7691,7 +9364,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="152" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:8" ht="27" customHeight="1">
       <c r="B152" s="8" t="s">
         <v>553</v>
       </c>
@@ -7714,7 +9387,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="153" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:8" ht="27" customHeight="1">
       <c r="B153" s="5" t="s">
         <v>555</v>
       </c>
@@ -7737,7 +9410,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="154" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:8" ht="27" customHeight="1">
       <c r="B154" s="8" t="s">
         <v>558</v>
       </c>
@@ -7760,7 +9433,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="155" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:8" ht="27" customHeight="1">
       <c r="B155" s="5" t="s">
         <v>564</v>
       </c>
@@ -7783,7 +9456,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="156" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:8" ht="27" customHeight="1">
       <c r="B156" s="8" t="s">
         <v>569</v>
       </c>
@@ -7806,7 +9479,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="157" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" ht="27" customHeight="1">
       <c r="B157" s="5" t="s">
         <v>573</v>
       </c>
@@ -7829,7 +9502,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="158" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:8" ht="27" customHeight="1">
       <c r="B158" s="8" t="s">
         <v>577</v>
       </c>
@@ -7852,7 +9525,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="159" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:8" ht="27" customHeight="1">
       <c r="B159" s="5" t="s">
         <v>579</v>
       </c>
@@ -7875,7 +9548,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="160" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:8" ht="27" customHeight="1">
       <c r="B160" s="8" t="s">
         <v>581</v>
       </c>
@@ -7898,7 +9571,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="161" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:8" ht="27" customHeight="1">
       <c r="B161" s="5" t="s">
         <v>584</v>
       </c>
@@ -7921,7 +9594,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="162" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:8" ht="27" customHeight="1">
       <c r="B162" s="8" t="s">
         <v>588</v>
       </c>
@@ -7944,7 +9617,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="163" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:8" ht="27" customHeight="1">
       <c r="B163" s="5" t="s">
         <v>590</v>
       </c>
@@ -7967,7 +9640,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="164" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:8" ht="27" customHeight="1">
       <c r="B164" s="8" t="s">
         <v>592</v>
       </c>
@@ -7990,7 +9663,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="165" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:8" ht="27" customHeight="1">
       <c r="B165" s="5" t="s">
         <v>594</v>
       </c>
@@ -8013,7 +9686,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="166" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:8" ht="27" customHeight="1">
       <c r="B166" s="8" t="s">
         <v>596</v>
       </c>
@@ -8036,7 +9709,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="167" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:8" ht="27" customHeight="1">
       <c r="B167" s="5" t="s">
         <v>599</v>
       </c>
@@ -8059,7 +9732,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="168" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:8" ht="27" customHeight="1">
       <c r="B168" s="8" t="s">
         <v>603</v>
       </c>
@@ -8082,7 +9755,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="169" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:8" ht="27" customHeight="1">
       <c r="B169" s="5" t="s">
         <v>606</v>
       </c>
@@ -8105,7 +9778,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="170" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:8" ht="27" customHeight="1">
       <c r="B170" s="8" t="s">
         <v>609</v>
       </c>
@@ -8128,7 +9801,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="171" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:8" ht="27" customHeight="1">
       <c r="B171" s="5" t="s">
         <v>612</v>
       </c>
@@ -8151,7 +9824,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="172" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:8" ht="27" customHeight="1">
       <c r="B172" s="8" t="s">
         <v>615</v>
       </c>
@@ -8174,7 +9847,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="173" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:8" ht="27" customHeight="1">
       <c r="B173" s="5" t="s">
         <v>618</v>
       </c>
@@ -8197,7 +9870,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="174" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:8" ht="27" customHeight="1">
       <c r="B174" s="8" t="s">
         <v>624</v>
       </c>
@@ -8220,7 +9893,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="175" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:8" ht="27" customHeight="1">
       <c r="B175" s="5" t="s">
         <v>629</v>
       </c>
@@ -8243,7 +9916,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="176" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:8" ht="27" customHeight="1">
       <c r="B176" s="8" t="s">
         <v>632</v>
       </c>
@@ -8266,7 +9939,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="177" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:8" ht="27" customHeight="1">
       <c r="B177" s="5" t="s">
         <v>636</v>
       </c>
@@ -8289,7 +9962,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="178" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:8" ht="27" customHeight="1">
       <c r="B178" s="8" t="s">
         <v>640</v>
       </c>
@@ -8312,7 +9985,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="179" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:8" ht="27" customHeight="1">
       <c r="B179" s="5" t="s">
         <v>644</v>
       </c>
@@ -8335,7 +10008,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="180" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:8" ht="27" customHeight="1">
       <c r="B180" s="8" t="s">
         <v>649</v>
       </c>
@@ -8358,7 +10031,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="181" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:8" ht="27" customHeight="1">
       <c r="B181" s="5" t="s">
         <v>652</v>
       </c>
@@ -8381,7 +10054,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="182" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:8" ht="27" customHeight="1">
       <c r="B182" s="8" t="s">
         <v>656</v>
       </c>
@@ -8404,7 +10077,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="183" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:8" ht="27" customHeight="1">
       <c r="B183" s="5" t="s">
         <v>660</v>
       </c>
@@ -8427,7 +10100,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="184" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:8" ht="27" customHeight="1">
       <c r="B184" s="8" t="s">
         <v>665</v>
       </c>
@@ -8450,7 +10123,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="185" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:8" ht="27" customHeight="1">
       <c r="B185" s="5" t="s">
         <v>669</v>
       </c>
@@ -8473,7 +10146,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="186" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:8" ht="27" customHeight="1">
       <c r="B186" s="8" t="s">
         <v>674</v>
       </c>
@@ -8496,7 +10169,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="187" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:8" ht="27" customHeight="1">
       <c r="B187" s="5" t="s">
         <v>678</v>
       </c>
@@ -8519,7 +10192,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="188" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:8" ht="27" customHeight="1">
       <c r="B188" s="8" t="s">
         <v>682</v>
       </c>
@@ -8542,7 +10215,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="189" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:8" ht="27" customHeight="1">
       <c r="B189" s="5" t="s">
         <v>684</v>
       </c>
@@ -8565,7 +10238,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="190" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:8" ht="27" customHeight="1">
       <c r="B190" s="8" t="s">
         <v>686</v>
       </c>
@@ -8588,7 +10261,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="191" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:8" ht="27" customHeight="1">
       <c r="B191" s="5" t="s">
         <v>689</v>
       </c>
@@ -8611,7 +10284,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="192" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:8" ht="27" customHeight="1">
       <c r="B192" s="8" t="s">
         <v>695</v>
       </c>
@@ -8634,7 +10307,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="193" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:8" ht="27" customHeight="1">
       <c r="B193" s="5" t="s">
         <v>699</v>
       </c>
@@ -8657,7 +10330,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="194" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:8" ht="27" customHeight="1">
       <c r="B194" s="8" t="s">
         <v>703</v>
       </c>
@@ -8680,7 +10353,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="195" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:8" ht="27" customHeight="1">
       <c r="B195" s="5" t="s">
         <v>707</v>
       </c>
@@ -8703,7 +10376,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="196" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:8" ht="27" customHeight="1">
       <c r="B196" s="8" t="s">
         <v>712</v>
       </c>
@@ -8726,7 +10399,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="197" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:8" ht="27" customHeight="1">
       <c r="B197" s="5" t="s">
         <v>714</v>
       </c>
@@ -8749,7 +10422,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="198" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:8" ht="27" customHeight="1">
       <c r="B198" s="8" t="s">
         <v>719</v>
       </c>
@@ -8772,7 +10445,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="199" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:8" ht="27" customHeight="1">
       <c r="B199" s="5" t="s">
         <v>724</v>
       </c>
@@ -8795,7 +10468,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="200" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:8" ht="27" customHeight="1">
       <c r="B200" s="8" t="s">
         <v>728</v>
       </c>
@@ -8818,7 +10491,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="201" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:8" ht="27" customHeight="1">
       <c r="B201" s="5" t="s">
         <v>732</v>
       </c>
@@ -8841,7 +10514,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="202" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:8" ht="27" customHeight="1">
       <c r="B202" s="8" t="s">
         <v>737</v>
       </c>
@@ -8864,7 +10537,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="203" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:8" ht="27" customHeight="1">
       <c r="B203" s="5" t="s">
         <v>741</v>
       </c>
@@ -8887,7 +10560,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="204" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:8" ht="27" customHeight="1">
       <c r="B204" s="8" t="s">
         <v>745</v>
       </c>
@@ -8910,7 +10583,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="205" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:8" ht="27" customHeight="1">
       <c r="B205" s="5" t="s">
         <v>749</v>
       </c>
@@ -8933,7 +10606,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="206" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:8" ht="27" customHeight="1">
       <c r="B206" s="8" t="s">
         <v>754</v>
       </c>
@@ -8956,7 +10629,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="207" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:8" ht="27" customHeight="1">
       <c r="B207" s="5" t="s">
         <v>757</v>
       </c>
@@ -8979,7 +10652,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="208" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:8" ht="27" customHeight="1">
       <c r="B208" s="8" t="s">
         <v>759</v>
       </c>
@@ -9002,7 +10675,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="209" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:8" ht="27" customHeight="1">
       <c r="B209" s="5" t="s">
         <v>761</v>
       </c>
@@ -9025,7 +10698,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="210" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:8" ht="27" customHeight="1">
       <c r="B210" s="8" t="s">
         <v>764</v>
       </c>
@@ -9048,7 +10721,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="211" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:8" ht="27" customHeight="1">
       <c r="B211" s="5" t="s">
         <v>770</v>
       </c>
@@ -9071,7 +10744,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="212" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:8" ht="27" customHeight="1">
       <c r="B212" s="8" t="s">
         <v>775</v>
       </c>
@@ -9094,7 +10767,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="213" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:8" ht="27" customHeight="1">
       <c r="B213" s="5" t="s">
         <v>778</v>
       </c>
@@ -9117,7 +10790,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="214" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:8" ht="27" customHeight="1">
       <c r="B214" s="8" t="s">
         <v>782</v>
       </c>
@@ -9140,7 +10813,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="215" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:8" ht="27" customHeight="1">
       <c r="B215" s="5" t="s">
         <v>786</v>
       </c>
@@ -9163,7 +10836,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="216" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:8" ht="27" customHeight="1">
       <c r="B216" s="8" t="s">
         <v>791</v>
       </c>
@@ -9186,7 +10859,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="217" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:8" ht="27" customHeight="1">
       <c r="B217" s="5" t="s">
         <v>794</v>
       </c>
@@ -9209,7 +10882,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="218" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:8" ht="27" customHeight="1">
       <c r="B218" s="11" t="s">
         <v>798</v>
       </c>
@@ -9232,7 +10905,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="219" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:8" ht="27" customHeight="1">
       <c r="B219" s="14" t="s">
         <v>800</v>
       </c>
@@ -9255,7 +10928,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="220" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:8" ht="27" customHeight="1">
       <c r="B220" s="11" t="s">
         <v>802</v>
       </c>
@@ -9278,7 +10951,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="221" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:8" ht="27" customHeight="1">
       <c r="B221" s="14" t="s">
         <v>804</v>
       </c>
@@ -9301,7 +10974,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="222" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:8" ht="27" customHeight="1">
       <c r="B222" t="s">
         <v>808</v>
       </c>
@@ -9324,7 +10997,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="223" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:8" ht="27" customHeight="1">
       <c r="B223" t="s">
         <v>810</v>
       </c>
@@ -9347,7 +11020,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="224" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:8" ht="30" customHeight="1">
       <c r="B224" t="s">
         <v>812</v>
       </c>
@@ -9370,7 +11043,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="225" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:9" ht="27" customHeight="1">
       <c r="B225" t="s">
         <v>816</v>
       </c>
@@ -9396,7 +11069,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="226" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:9" ht="27" customHeight="1">
       <c r="B226" t="s">
         <v>822</v>
       </c>
@@ -9419,7 +11092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="227" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:9" ht="27" customHeight="1">
       <c r="B227" t="s">
         <v>825</v>
       </c>
@@ -9442,7 +11115,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="228" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:9" ht="27" customHeight="1">
       <c r="B228" t="s">
         <v>828</v>
       </c>
@@ -9465,7 +11138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:9" ht="27" customHeight="1">
       <c r="B229" t="s">
         <v>831</v>
       </c>
@@ -9488,7 +11161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="230" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:9" ht="27" customHeight="1">
       <c r="B230" t="s">
         <v>834</v>
       </c>
@@ -9511,7 +11184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="231" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:9" ht="27" customHeight="1">
       <c r="B231" t="s">
         <v>839</v>
       </c>
@@ -9534,7 +11207,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="232" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:9" ht="27" customHeight="1">
       <c r="B232" t="s">
         <v>844</v>
       </c>
@@ -9557,7 +11230,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="233" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:9" ht="27" customHeight="1">
       <c r="B233" t="s">
         <v>849</v>
       </c>
@@ -9580,7 +11253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:9" ht="27" customHeight="1">
       <c r="B234" t="s">
         <v>852</v>
       </c>
@@ -9603,7 +11276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="235" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:9" ht="27" customHeight="1">
       <c r="B235" t="s">
         <v>855</v>
       </c>
@@ -9626,7 +11299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:9" ht="27" customHeight="1">
       <c r="B236" t="s">
         <v>858</v>
       </c>
@@ -9649,7 +11322,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:9" ht="27" customHeight="1">
       <c r="B237" t="s">
         <v>861</v>
       </c>
@@ -9672,7 +11345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:9" ht="27" customHeight="1">
       <c r="B238" t="s">
         <v>864</v>
       </c>
@@ -9695,7 +11368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="239" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:9" ht="27" customHeight="1">
       <c r="B239" t="s">
         <v>865</v>
       </c>
@@ -9718,7 +11391,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:9" ht="27" customHeight="1">
       <c r="B240" t="s">
         <v>867</v>
       </c>
@@ -9741,7 +11414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:8" ht="27" customHeight="1">
       <c r="B241" t="s">
         <v>868</v>
       </c>
@@ -9764,7 +11437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:8" ht="27" customHeight="1">
       <c r="B242" t="s">
         <v>870</v>
       </c>
@@ -9787,7 +11460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="243" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:8" ht="27" customHeight="1">
       <c r="B243" t="s">
         <v>871</v>
       </c>
@@ -9810,7 +11483,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="244" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:8" ht="27" customHeight="1">
       <c r="B244" t="s">
         <v>873</v>
       </c>
@@ -9833,7 +11506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="245" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:8" ht="27" customHeight="1">
       <c r="B245" t="s">
         <v>874</v>
       </c>
@@ -9856,7 +11529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="246" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:8" ht="27" customHeight="1">
       <c r="B246" t="s">
         <v>876</v>
       </c>
@@ -9879,7 +11552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:8" ht="27" customHeight="1">
       <c r="B247" t="s">
         <v>877</v>
       </c>
@@ -9902,7 +11575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="248" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:8" ht="27" customHeight="1">
       <c r="B248" t="s">
         <v>880</v>
       </c>
@@ -9925,7 +11598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="249" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:8" ht="27" customHeight="1">
       <c r="B249" t="s">
         <v>883</v>
       </c>
@@ -9948,7 +11621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="250" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:8" ht="27" customHeight="1">
       <c r="B250" t="s">
         <v>886</v>
       </c>
@@ -9971,7 +11644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="251" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:8" ht="27" customHeight="1">
       <c r="B251" t="s">
         <v>889</v>
       </c>
@@ -9994,7 +11667,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:8" ht="27" customHeight="1">
       <c r="B252" t="s">
         <v>891</v>
       </c>
@@ -10017,7 +11690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="253" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:8" ht="27" customHeight="1">
       <c r="B253" t="s">
         <v>894</v>
       </c>
@@ -10040,7 +11713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="254" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:8" ht="27" customHeight="1">
       <c r="B254" t="s">
         <v>897</v>
       </c>
@@ -10063,7 +11736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:8" ht="27" customHeight="1">
       <c r="B255" t="s">
         <v>901</v>
       </c>
@@ -10086,7 +11759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="256" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:8" ht="27" customHeight="1">
       <c r="B256" t="s">
         <v>905</v>
       </c>
@@ -10109,7 +11782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="257" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:8" ht="27" customHeight="1">
       <c r="B257" t="s">
         <v>907</v>
       </c>
@@ -10132,7 +11805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:8" ht="27" customHeight="1">
       <c r="B258" t="s">
         <v>910</v>
       </c>
@@ -10155,7 +11828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="259" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:8" ht="27" customHeight="1">
       <c r="B259" t="s">
         <v>915</v>
       </c>
@@ -10178,7 +11851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="260" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:8" ht="27" customHeight="1">
       <c r="B260" t="s">
         <v>919</v>
       </c>
@@ -10201,7 +11874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:8" ht="27" customHeight="1">
       <c r="B261" t="s">
         <v>923</v>
       </c>
@@ -10224,7 +11897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="262" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:8" ht="27" customHeight="1">
       <c r="B262" t="s">
         <v>927</v>
       </c>
@@ -10247,7 +11920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="263" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:8" ht="27" customHeight="1">
       <c r="B263" t="s">
         <v>931</v>
       </c>
@@ -10270,7 +11943,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="264" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:8" ht="27" customHeight="1">
       <c r="B264" t="s">
         <v>933</v>
       </c>
@@ -10293,7 +11966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="265" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:8" ht="27" customHeight="1">
       <c r="B265" t="s">
         <v>936</v>
       </c>
@@ -10316,7 +11989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="266" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:8" ht="27" customHeight="1">
       <c r="B266" t="s">
         <v>939</v>
       </c>
@@ -10339,7 +12012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="267" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:8" ht="27" customHeight="1">
       <c r="B267" t="s">
         <v>942</v>
       </c>
@@ -10362,7 +12035,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:8" ht="27" customHeight="1">
       <c r="B268" t="s">
         <v>945</v>
       </c>
@@ -10385,7 +12058,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="269" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:8" ht="27" customHeight="1">
       <c r="B269" t="s">
         <v>948</v>
       </c>
@@ -10408,7 +12081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="270" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:8" ht="27" customHeight="1">
       <c r="B270" t="s">
         <v>950</v>
       </c>
@@ -10431,7 +12104,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:8" ht="27" customHeight="1">
       <c r="B271" t="s">
         <v>952</v>
       </c>
@@ -10454,7 +12127,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="272" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:8" ht="27" customHeight="1">
       <c r="B272" t="s">
         <v>955</v>
       </c>
@@ -10477,7 +12150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="273" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:8" ht="27" customHeight="1">
       <c r="B273" t="s">
         <v>957</v>
       </c>
@@ -10500,7 +12173,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:8" ht="27" customHeight="1">
       <c r="B274" t="s">
         <v>960</v>
       </c>
@@ -10523,7 +12196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="275" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:8" ht="27" customHeight="1">
       <c r="B275" t="s">
         <v>963</v>
       </c>
@@ -10546,7 +12219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:8" ht="27" customHeight="1">
       <c r="B276" t="s">
         <v>967</v>
       </c>
@@ -10569,7 +12242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="277" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:8" ht="27" customHeight="1">
       <c r="B277" t="s">
         <v>968</v>
       </c>
@@ -10592,7 +12265,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="278" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:8" ht="27" customHeight="1">
       <c r="B278" t="s">
         <v>971</v>
       </c>
@@ -10615,7 +12288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:8" ht="27" customHeight="1">
       <c r="B279" t="s">
         <v>974</v>
       </c>
@@ -10638,7 +12311,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="280" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:8" ht="27" customHeight="1">
       <c r="B280" t="s">
         <v>976</v>
       </c>
@@ -10661,7 +12334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="281" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:8" ht="27" customHeight="1">
       <c r="B281" s="19" t="s">
         <v>979</v>
       </c>
@@ -10684,7 +12357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="282" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:8" ht="27" customHeight="1">
       <c r="B282" s="19" t="s">
         <v>983</v>
       </c>
@@ -10707,7 +12380,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="283" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:8" ht="27" customHeight="1">
       <c r="B283" s="19" t="s">
         <v>988</v>
       </c>
@@ -10730,7 +12403,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="284" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:8" ht="27" customHeight="1">
       <c r="B284" s="19" t="s">
         <v>993</v>
       </c>
@@ -10753,7 +12426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="285" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:8" ht="27" customHeight="1">
       <c r="B285" s="19" t="s">
         <v>996</v>
       </c>
@@ -10776,7 +12449,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="286" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:8" ht="27" customHeight="1">
       <c r="B286" s="19" t="s">
         <v>998</v>
       </c>
@@ -10799,7 +12472,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="287" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:8" ht="27" customHeight="1">
       <c r="B287" s="19" t="s">
         <v>1002</v>
       </c>
@@ -10822,7 +12495,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="288" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:8" ht="27" customHeight="1">
       <c r="B288" s="19" t="s">
         <v>1004</v>
       </c>
@@ -10845,7 +12518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="289" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:9" ht="27" customHeight="1">
       <c r="B289" s="19" t="s">
         <v>1008</v>
       </c>
@@ -10868,7 +12541,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="290" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:9" ht="27" customHeight="1">
       <c r="B290" s="19" t="s">
         <v>1011</v>
       </c>
@@ -10891,7 +12564,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="291" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:9" ht="27" customHeight="1">
       <c r="B291" s="19" t="s">
         <v>1015</v>
       </c>
@@ -10914,7 +12587,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="292" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:9" ht="27" customHeight="1">
       <c r="B292" s="19" t="s">
         <v>1020</v>
       </c>
@@ -10937,7 +12610,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="293" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:9" ht="27" customHeight="1">
       <c r="B293" s="19" t="s">
         <v>1024</v>
       </c>
@@ -10960,7 +12633,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="294" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:9" ht="27" customHeight="1">
       <c r="B294" s="19" t="s">
         <v>1027</v>
       </c>
@@ -10983,7 +12656,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="295" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:9" ht="27" customHeight="1">
       <c r="B295" s="19" t="s">
         <v>1030</v>
       </c>
@@ -11006,7 +12679,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="296" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:9" ht="27" customHeight="1">
       <c r="B296" s="19" t="s">
         <v>1033</v>
       </c>
@@ -11029,7 +12702,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="297" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:9" ht="27" customHeight="1">
       <c r="B297" s="19" t="s">
         <v>1036</v>
       </c>
@@ -11052,7 +12725,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="298" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:9" ht="27" customHeight="1">
       <c r="B298" s="19" t="s">
         <v>1039</v>
       </c>
@@ -11075,7 +12748,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="299" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:9" ht="27" customHeight="1">
       <c r="B299" s="19" t="s">
         <v>1041</v>
       </c>
@@ -11098,7 +12771,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="300" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:9" ht="27" customHeight="1">
       <c r="B300" s="19" t="s">
         <v>1044</v>
       </c>
@@ -11121,7 +12794,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="301" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:9" ht="27" customHeight="1">
       <c r="B301" s="19" t="s">
         <v>1048</v>
       </c>
@@ -11144,7 +12817,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="302" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:9" ht="27" customHeight="1">
       <c r="B302" s="19" t="s">
         <v>1051</v>
       </c>
@@ -11167,7 +12840,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="303" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:9" ht="27" customHeight="1">
       <c r="B303" s="19" t="s">
         <v>1053</v>
       </c>
@@ -11188,6 +12861,331 @@
       </c>
       <c r="H303" s="19" t="s">
         <v>987</v>
+      </c>
+    </row>
+    <row r="304" spans="2:9" ht="27" customHeight="1">
+      <c r="B304" s="22" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C304" s="22" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D304" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E304" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F304" s="22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G304" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H304" s="22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I304" s="29" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="305" spans="2:8" ht="27" customHeight="1">
+      <c r="B305" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C305" s="22" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D305" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E305" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F305" s="22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G305" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H305" s="22" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="306" spans="2:8" ht="27" customHeight="1">
+      <c r="B306" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C306" s="22" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D306" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E306" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F306" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G306" s="22" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H306" s="22" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="307" spans="2:8" ht="27" customHeight="1">
+      <c r="B307" s="22" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C307" s="22" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D307" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E307" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F307" s="22" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G307" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H307" s="22" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="308" spans="2:8" ht="27" customHeight="1">
+      <c r="B308" s="22" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C308" s="22" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D308" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E308" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F308" s="22" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G308" s="22" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H308" s="22" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="309" spans="2:8" ht="27" customHeight="1">
+      <c r="B309" s="22" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C309" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D309" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E309" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F309" s="22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G309" s="22" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H309" s="22" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="310" spans="2:8" ht="27" customHeight="1">
+      <c r="B310" s="22" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C310" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D310" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E310" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F310" s="22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G310" s="22" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H310" s="22" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="311" spans="2:8" ht="27" customHeight="1">
+      <c r="B311" s="22" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C311" s="22" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D311" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E311" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F311" s="22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G311" s="22" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H311" s="22" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="312" spans="2:8" ht="27" customHeight="1">
+      <c r="B312" s="22" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C312" s="22" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D312" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E312" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F312" s="22" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G312" s="22" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H312" s="22" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="313" spans="2:8" ht="27" customHeight="1">
+      <c r="B313" s="22" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C313" s="22" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D313" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E313" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F313" s="22" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G313" s="22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H313" s="22" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="314" spans="2:8" ht="27" customHeight="1">
+      <c r="B314" s="22" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C314" s="22" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D314" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E314" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F314" s="22" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G314" s="22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H314" s="22" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="315" spans="2:8" ht="27" customHeight="1">
+      <c r="B315" s="22" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C315" s="22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D315" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E315" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F315" s="22" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G315" s="22" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H315" s="22" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="316" spans="2:8" ht="27" customHeight="1">
+      <c r="B316" s="22" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C316" s="22" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D316" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E316" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F316" s="22" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G316" s="22" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H316" s="22" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="317" spans="2:8" ht="27" customHeight="1">
+      <c r="B317" s="22" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C317" s="22" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D317" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E317" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F317" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G317" s="22" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H317" s="22" t="s">
+        <v>1162</v>
       </c>
     </row>
   </sheetData>
@@ -11197,4 +13195,506 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F4A9BD-7794-4489-887E-FDABC681ECDE}">
+  <dimension ref="B2:AV18"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetData>
+    <row r="2" spans="2:48" ht="17.149999999999999">
+      <c r="B2" s="23" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>1096</v>
+      </c>
+      <c r="Y2" s="23" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AH2" s="23" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AQ2" s="23" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="3" spans="2:48">
+      <c r="B3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AQ3" s="4"/>
+    </row>
+    <row r="4" spans="2:48">
+      <c r="B4" s="24" t="s">
+        <v>1066</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AH4" s="24" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AQ4" s="24" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="5" spans="2:48">
+      <c r="B5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="AH5" s="4"/>
+      <c r="AQ5" s="4"/>
+    </row>
+    <row r="6" spans="2:48">
+      <c r="B6" s="24" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Y6" s="24" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AH6" s="24" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AQ6" s="24" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="7" spans="2:48">
+      <c r="B7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="AH7" s="4"/>
+      <c r="AQ7" s="4"/>
+    </row>
+    <row r="8" spans="2:48">
+      <c r="B8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AQ8" s="25"/>
+    </row>
+    <row r="9" spans="2:48">
+      <c r="B9" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Y9" s="26" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AH9" s="26" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AQ9" s="26" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="10" spans="2:48">
+      <c r="B10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="AH10" s="27"/>
+      <c r="AQ10" s="27"/>
+    </row>
+    <row r="11" spans="2:48">
+      <c r="B11" s="26" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Y11" s="26" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AH11" s="26" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AQ11" s="26" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="14" spans="2:48" ht="56.6">
+      <c r="B14" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O14" s="20" t="s">
+        <v>1086</v>
+      </c>
+      <c r="P14" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="R14" s="20" t="s">
+        <v>1088</v>
+      </c>
+      <c r="S14" s="20" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Y14" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Z14" s="20" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AA14" s="20" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AB14" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AC14" s="20" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AD14" s="20" t="s">
+        <v>1056</v>
+      </c>
+      <c r="AH14" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AI14" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AJ14" s="20" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AK14" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AL14" s="20" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AM14" s="20" t="s">
+        <v>1056</v>
+      </c>
+      <c r="AQ14" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AR14" s="20" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AS14" s="20" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AT14" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AU14" s="20" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AV14" s="20" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="15" spans="2:48" ht="56.6">
+      <c r="B15" s="20" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>1090</v>
+      </c>
+      <c r="O15" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="P15" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>1081</v>
+      </c>
+      <c r="R15" s="22" t="s">
+        <v>1091</v>
+      </c>
+      <c r="S15" s="21" t="s">
+        <v>1059</v>
+      </c>
+      <c r="Y15" s="20" t="s">
+        <v>1102</v>
+      </c>
+      <c r="Z15" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AA15" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AB15" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AC15" s="22" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AD15" s="21" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AH15" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AI15" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AJ15" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AK15" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AL15" s="22" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AM15" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AQ15" s="20" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AR15" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AS15" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AT15" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AU15" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AV15" s="21" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="16" spans="2:48" ht="42.45">
+      <c r="B16" s="20" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>1063</v>
+      </c>
+      <c r="N16" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="O16" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P16" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="Q16" s="20" t="s">
+        <v>1081</v>
+      </c>
+      <c r="R16" s="22" t="s">
+        <v>1093</v>
+      </c>
+      <c r="S16" s="21" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Y16" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Z16" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AA16" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AB16" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AC16" s="22" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AD16" s="21" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AH16" s="20" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AI16" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AJ16" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AK16" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AL16" s="22" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AM16" s="21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AQ16" s="20" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AR16" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AS16" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AT16" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AU16" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AV16" s="21" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="17" spans="2:48" ht="42.45">
+      <c r="B17" s="20" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>1064</v>
+      </c>
+      <c r="N17" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="R17" s="22" t="s">
+        <v>1095</v>
+      </c>
+      <c r="S17" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="Y17" s="20" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AA17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AB17" s="20" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AC17" s="22" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AD17" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AH17" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="AI17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AJ17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AK17" s="20" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AL17" s="22" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AM17" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AQ17" s="20" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AR17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AS17" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AT17" s="20" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AU17" s="22" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AV17" s="21" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="18" spans="2:48" ht="42.45">
+      <c r="B18" s="20" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/GreenHerb/Matriz de rastreabilidade.xlsx
+++ b/GreenHerb/Matriz de rastreabilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\GreenHerb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E88105C-86B8-401B-934B-8A57215A0698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA37AA3-F06C-49E6-952D-3D2CF0254B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testes" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="1207">
   <si>
     <t>ID</t>
   </si>
@@ -4775,6 +4775,65 @@
   </si>
   <si>
     <t>Sprint 5</t>
+  </si>
+  <si>
+    <t>RN-02: Intervalo Correto de Temperatura.</t>
+  </si>
+  <si>
+    <r>
+      <t>Sucesso (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>valid: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).Criação do Plano</t>
+    </r>
+  </si>
+  <si>
+    <t>TU-WB-15</t>
+  </si>
+  <si>
+    <t>TU-WB-16</t>
+  </si>
+  <si>
+    <t>RN-02: Intervalo Correto de Humidade.</t>
+  </si>
+  <si>
+    <t>TU-WB-17</t>
+  </si>
+  <si>
+    <t>RN-02: Intervalo Correto de Luminosidade.</t>
+  </si>
+  <si>
+    <t>TU-WB-18</t>
+  </si>
+  <si>
+    <t>RN-02: Intervalo Correto de Duração.</t>
+  </si>
+  <si>
+    <t>TU-WB-015</t>
+  </si>
+  <si>
+    <t>TU-WB-016</t>
+  </si>
+  <si>
+    <t>TU-WB-017</t>
+  </si>
+  <si>
+    <t>TU-WB-018</t>
   </si>
 </sst>
 </file>
@@ -4884,7 +4943,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4911,6 +4970,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4967,7 +5032,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5048,6 +5113,12 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Neutral" xfId="3" xr:uid="{21D3CBB1-B351-413A-B518-A23BC59AF63F}"/>
@@ -5087,8 +5158,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H317" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B3:H317" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="B3:H318" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B3:H318" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requisito / Regra"/>
@@ -5419,7 +5490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U317"/>
+  <dimension ref="B1:U321"/>
   <sheetFormatPr defaultColWidth="8.15234375" defaultRowHeight="27" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -13186,6 +13257,98 @@
       </c>
       <c r="H317" s="22" t="s">
         <v>1162</v>
+      </c>
+    </row>
+    <row r="318" spans="2:8" ht="27" customHeight="1">
+      <c r="B318" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C318" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D318" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E318" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F318" s="22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G318" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H318" s="22" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="319" spans="2:8" ht="27" customHeight="1">
+      <c r="B319" s="22" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C319" s="22" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D319" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E319" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F319" s="22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G319" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H319" s="22" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="320" spans="2:8" ht="27" customHeight="1">
+      <c r="B320" s="30" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C320" s="30" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D320" s="31" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E320" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F320" s="30" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G320" s="30" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H320" s="30" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="321" spans="2:8" ht="27" customHeight="1">
+      <c r="B321" s="22" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C321" s="22" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D321" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E321" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F321" s="22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G321" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H321" s="22" t="s">
+        <v>1195</v>
       </c>
     </row>
   </sheetData>
@@ -13588,7 +13751,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="2:48" ht="42.45">
+    <row r="17" spans="2:48" ht="56.6">
       <c r="B17" s="20" t="s">
         <v>1080</v>
       </c>
@@ -13620,7 +13783,7 @@
         <v>1095</v>
       </c>
       <c r="S17" s="21" t="s">
-        <v>1062</v>
+        <v>1203</v>
       </c>
       <c r="Y17" s="20" t="s">
         <v>1108</v>
@@ -13638,7 +13801,7 @@
         <v>1110</v>
       </c>
       <c r="AD17" s="21" t="s">
-        <v>1062</v>
+        <v>1204</v>
       </c>
       <c r="AH17" s="20" t="s">
         <v>1125</v>
@@ -13656,7 +13819,7 @@
         <v>1126</v>
       </c>
       <c r="AM17" s="21" t="s">
-        <v>1062</v>
+        <v>1205</v>
       </c>
       <c r="AQ17" s="20" t="s">
         <v>1139</v>
@@ -13674,7 +13837,7 @@
         <v>1140</v>
       </c>
       <c r="AV17" s="21" t="s">
-        <v>1062</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="18" spans="2:48" ht="42.45">
